--- a/doc/六分厂6-1#装配线/点位信息.xlsx
+++ b/doc/六分厂6-1#装配线/点位信息.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Sheet3" sheetId="7" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$3:$D$26</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="109">
   <si>
     <t>设备名称</t>
   </si>
@@ -44,7 +44,7 @@
     <t>PLC_Port</t>
   </si>
   <si>
-    <t>点位名称</t>
+    <t xml:space="preserve">  </t>
   </si>
   <si>
     <t>描述</t>
@@ -104,129 +104,111 @@
     <t>NG代码A</t>
   </si>
   <si>
-    <t>小内圈分选数据</t>
+    <t>A面钢球组差</t>
+  </si>
+  <si>
+    <t>UInt16</t>
+  </si>
+  <si>
+    <t>B面钢球组差</t>
+  </si>
+  <si>
+    <t>A面钢球注脂量</t>
+  </si>
+  <si>
+    <t>({0}/100)</t>
+  </si>
+  <si>
+    <t>密封圈平行差</t>
   </si>
   <si>
     <t>({0}/1000)</t>
   </si>
   <si>
-    <t>外法兰分选数据</t>
-  </si>
-  <si>
-    <t>内法兰分选数据</t>
-  </si>
-  <si>
-    <t>A面钢球组差</t>
-  </si>
-  <si>
-    <t>UInt16</t>
-  </si>
-  <si>
-    <t>B面钢球组差</t>
-  </si>
-  <si>
-    <t>A面钢球注脂量</t>
-  </si>
-  <si>
-    <t>({0}/100)</t>
-  </si>
-  <si>
-    <t>密封圈压装力</t>
+    <t>B面钢球注脂量</t>
+  </si>
+  <si>
+    <t>外法兰半成品码</t>
+  </si>
+  <si>
+    <t>String</t>
+  </si>
+  <si>
+    <t>内法兰半成品码</t>
+  </si>
+  <si>
+    <t>六分厂6-1装配B线</t>
+  </si>
+  <si>
+    <t>100.100.100.6</t>
+  </si>
+  <si>
+    <t>58D</t>
+  </si>
+  <si>
+    <t>序列码</t>
+  </si>
+  <si>
+    <t>ABS检测齿数</t>
+  </si>
+  <si>
+    <t>托盘号B</t>
+  </si>
+  <si>
+    <t>型号B</t>
+  </si>
+  <si>
+    <t>屏蔽工位B</t>
+  </si>
+  <si>
+    <t>NG代码B</t>
+  </si>
+  <si>
+    <t>A线托盘编号</t>
+  </si>
+  <si>
+    <t>识别代码</t>
+  </si>
+  <si>
+    <t>UInt32</t>
+  </si>
+  <si>
+    <t>正游隙检测值</t>
+  </si>
+  <si>
+    <t>负游隙检测值</t>
+  </si>
+  <si>
+    <t>位移量</t>
+  </si>
+  <si>
+    <t>铆接前成型高度</t>
+  </si>
+  <si>
+    <t>密封圈压装压力</t>
   </si>
   <si>
     <t>Single</t>
   </si>
   <si>
-    <t>密封圈压装位移A</t>
-  </si>
-  <si>
-    <t>密封圈平行差</t>
-  </si>
-  <si>
-    <t>密封圈注脂量</t>
+    <t>密封圈压装位移B</t>
+  </si>
+  <si>
+    <t>磁性圈平行差检测传感器1</t>
+  </si>
+  <si>
+    <t>磁性圈平行差检测传感器2</t>
+  </si>
+  <si>
+    <t>磁性圈平行差检测传感器3</t>
+  </si>
+  <si>
+    <t>振动下LOAD</t>
   </si>
   <si>
     <t>({0}/10)</t>
   </si>
   <si>
-    <t>B面钢球注脂量</t>
-  </si>
-  <si>
-    <t>外法兰半成品码</t>
-  </si>
-  <si>
-    <t>String</t>
-  </si>
-  <si>
-    <t>内法兰半成品码</t>
-  </si>
-  <si>
-    <t>六分厂6-1装配B线</t>
-  </si>
-  <si>
-    <t>100.100.100.6</t>
-  </si>
-  <si>
-    <t>58D</t>
-  </si>
-  <si>
-    <t>序列码</t>
-  </si>
-  <si>
-    <t>ABS检测齿数</t>
-  </si>
-  <si>
-    <t>托盘号B</t>
-  </si>
-  <si>
-    <t>型号B</t>
-  </si>
-  <si>
-    <t>屏蔽工位B</t>
-  </si>
-  <si>
-    <t>NG代码B</t>
-  </si>
-  <si>
-    <t>A线托盘编号</t>
-  </si>
-  <si>
-    <t>识别代码</t>
-  </si>
-  <si>
-    <t>UInt32</t>
-  </si>
-  <si>
-    <t>正游隙检测值</t>
-  </si>
-  <si>
-    <t>位移量</t>
-  </si>
-  <si>
-    <t>负游隙检测值</t>
-  </si>
-  <si>
-    <t>铆接前成型高度</t>
-  </si>
-  <si>
-    <t>密封圈压装压力</t>
-  </si>
-  <si>
-    <t>密封圈压装位移B</t>
-  </si>
-  <si>
-    <t>磁性圈平行差检测传感器1</t>
-  </si>
-  <si>
-    <t>磁性圈平行差检测传感器2</t>
-  </si>
-  <si>
-    <t>磁性圈平行差检测传感器3</t>
-  </si>
-  <si>
-    <t>振动下LOAD</t>
-  </si>
-  <si>
     <t>振动下LH</t>
   </si>
   <si>
@@ -236,6 +218,15 @@
     <t>振动下RH</t>
   </si>
   <si>
+    <t>振动上LOAD</t>
+  </si>
+  <si>
+    <t>振动上LH</t>
+  </si>
+  <si>
+    <t>振动上RH</t>
+  </si>
+  <si>
     <t>ABS检测峰值</t>
   </si>
   <si>
@@ -245,10 +236,55 @@
     <t>径跳值</t>
   </si>
   <si>
+    <t>磁性圈平行差</t>
+  </si>
+  <si>
+    <t>端跳值轴</t>
+  </si>
+  <si>
+    <t>端跳值平面</t>
+  </si>
+  <si>
+    <t>端跳值高度</t>
+  </si>
+  <si>
+    <t>1400 TQ</t>
+  </si>
+  <si>
+    <t>1400 M/HIGH</t>
+  </si>
+  <si>
+    <t>1600 P/M1400=ABSSINGLE MAX</t>
+  </si>
+  <si>
+    <t>1600 P/M1400=ABSSINGLE min</t>
+  </si>
+  <si>
+    <t>1600 P/M1400=ABSTOTAL</t>
+  </si>
+  <si>
+    <t>1600 P/M1400=ABSTOOTH</t>
+  </si>
+  <si>
+    <t>震动检测结果</t>
+  </si>
+  <si>
+    <t>跳动检测值</t>
+  </si>
+  <si>
+    <t>扁平度</t>
+  </si>
+  <si>
+    <t>高度上限</t>
+  </si>
+  <si>
+    <t>实测间隙</t>
+  </si>
+  <si>
+    <t>1150 GONO CHECK</t>
+  </si>
+  <si>
     <t>B线</t>
-  </si>
-  <si>
-    <t>磁性圈平行差</t>
   </si>
   <si>
     <t>防尘盖压装压力</t>
@@ -1030,7 +1066,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1070,15 +1106,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1088,9 +1118,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1127,9 +1154,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1169,41 +1193,44 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1525,1334 +1552,1608 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:K56"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="14.875" customWidth="1"/>
     <col min="3" max="3" width="13.5" customWidth="1"/>
-    <col min="4" max="4" width="24.5" style="31" customWidth="1"/>
+    <col min="4" max="4" width="24.5" style="28" customWidth="1"/>
     <col min="5" max="5" width="8.375" customWidth="1"/>
     <col min="6" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="7" width="10.25" style="43" customWidth="1"/>
+    <col min="7" max="7" width="10.25" style="39" customWidth="1"/>
     <col min="8" max="8" width="9.875" customWidth="1"/>
     <col min="9" max="9" width="7.375" customWidth="1"/>
     <col min="10" max="10" width="12.625" customWidth="1"/>
-    <col min="11" max="11" width="12.625" style="26" customWidth="1"/>
-    <col min="12" max="12" width="9" style="22"/>
-    <col min="14" max="14" width="25.625" customWidth="1"/>
+    <col min="11" max="11" width="12.625" style="23" customWidth="1"/>
+    <col min="13" max="13" width="25.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:12">
-      <c r="A1" s="44" t="s">
+    <row r="1" ht="14.25" spans="1:11">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="44" t="s">
+      <c r="B1" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="45" t="s">
+      <c r="D1" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="44" t="s">
+      <c r="E1" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="44" t="s">
+      <c r="F1" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="46" t="s">
+      <c r="G1" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="44" t="s">
+      <c r="H1" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="44" t="s">
+      <c r="I1" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="44" t="s">
+      <c r="J1" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="47" t="s">
+      <c r="K1" s="42" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" ht="15" spans="1:12">
-      <c r="A2" s="28" t="s">
+    <row r="2" ht="15" spans="1:11">
+      <c r="A2" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="35">
+      <c r="C2" s="31">
         <v>8001</v>
       </c>
-      <c r="D2" s="48" t="s">
+      <c r="D2" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="F2" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="43">
+      <c r="G2" s="39">
         <v>594</v>
       </c>
-      <c r="H2" s="23" t="s">
+      <c r="H2" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="23">
-        <v>1</v>
-      </c>
-      <c r="J2" s="22"/>
-    </row>
-    <row r="3" ht="15" spans="1:12">
-      <c r="A3" s="28" t="s">
+      <c r="I2" s="20">
+        <v>1</v>
+      </c>
+      <c r="J2" s="19"/>
+    </row>
+    <row r="3" ht="15" spans="1:11">
+      <c r="A3" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="35">
+      <c r="C3" s="31">
         <v>8001</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="D3" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="35" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="43">
+      <c r="F3" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="39">
         <v>24000</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="H3" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="22">
-        <v>1</v>
-      </c>
-      <c r="J3" s="22"/>
-    </row>
-    <row r="4" ht="15" spans="1:12">
-      <c r="A4" s="28" t="s">
+      <c r="I3" s="19">
+        <v>1</v>
+      </c>
+      <c r="J3" s="19"/>
+    </row>
+    <row r="4" ht="15" spans="1:11">
+      <c r="A4" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="35">
+      <c r="C4" s="31">
         <v>8001</v>
       </c>
-      <c r="D4" s="49" t="s">
+      <c r="D4" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="35" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="43">
+      <c r="F4" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="39">
         <v>24001</v>
       </c>
-      <c r="H4" s="22" t="s">
+      <c r="H4" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="22">
-        <v>1</v>
-      </c>
-      <c r="J4" s="22"/>
-    </row>
-    <row r="5" ht="15" spans="1:12">
-      <c r="A5" s="28" t="s">
+      <c r="I4" s="19">
+        <v>1</v>
+      </c>
+      <c r="J4" s="19"/>
+    </row>
+    <row r="5" ht="15" spans="1:11">
+      <c r="A5" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="35">
+      <c r="C5" s="31">
         <v>8001</v>
       </c>
-      <c r="D5" s="49" t="s">
+      <c r="D5" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="43">
+      <c r="F5" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="39">
         <v>24002</v>
       </c>
-      <c r="H5" s="22" t="s">
+      <c r="H5" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="I5" s="22">
-        <v>1</v>
-      </c>
-      <c r="J5" s="22"/>
-    </row>
-    <row r="6" ht="15" spans="1:12">
-      <c r="A6" s="28" t="s">
+      <c r="I5" s="19">
+        <v>1</v>
+      </c>
+      <c r="J5" s="19"/>
+    </row>
+    <row r="6" ht="15" spans="1:11">
+      <c r="A6" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="35">
+      <c r="C6" s="31">
         <v>8001</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="35" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="43">
+      <c r="F6" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="39">
         <v>24004</v>
       </c>
-      <c r="H6" s="22" t="s">
+      <c r="H6" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="22">
-        <v>1</v>
-      </c>
-      <c r="J6" s="22"/>
-    </row>
-    <row r="7" s="1" customFormat="1" ht="15" spans="1:12">
-      <c r="A7" s="32" t="s">
+      <c r="I6" s="19">
+        <v>1</v>
+      </c>
+      <c r="J6" s="19"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="15" spans="1:11">
+      <c r="A7" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="33">
+      <c r="C7" s="31">
         <v>8001</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" s="19">
-        <v>24005</v>
-      </c>
-      <c r="H7" s="50" t="s">
+      <c r="E7" s="20"/>
+      <c r="F7" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="39">
+        <v>24008</v>
+      </c>
+      <c r="H7" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="23"/>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="15" spans="1:11">
+      <c r="A8" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="31">
+        <v>8001</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="20"/>
+      <c r="F8" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="39">
+        <v>24009</v>
+      </c>
+      <c r="H8" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" s="19"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="23"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="15" spans="1:11">
+      <c r="A9" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="31">
+        <v>8001</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="20"/>
+      <c r="F9" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" s="39">
+        <v>24039</v>
+      </c>
+      <c r="H9" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="I7" s="6">
-        <v>1</v>
-      </c>
-      <c r="J7" s="11" t="s">
+      <c r="I9" s="20">
+        <v>1</v>
+      </c>
+      <c r="J9" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="K9" s="23"/>
+    </row>
+    <row r="10" ht="15" spans="1:11">
+      <c r="A10" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="31">
+        <v>8001</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="20"/>
+      <c r="F10" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" s="39">
+        <v>24031</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" s="20">
+        <v>1</v>
+      </c>
+      <c r="J10" s="24" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" ht="15" spans="1:11">
+      <c r="A11" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="31">
+        <v>8001</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="39">
+        <v>24012</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" s="20">
+        <v>1</v>
+      </c>
+      <c r="J11" s="24" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" ht="15" spans="1:11">
+      <c r="A12" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="31">
+        <v>8001</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="20"/>
+      <c r="F12" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" s="43">
+        <v>24074</v>
+      </c>
+      <c r="H12" s="44" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="20">
+        <v>18</v>
+      </c>
+      <c r="J12" s="24"/>
+      <c r="K12" s="38"/>
+    </row>
+    <row r="13" ht="15" spans="1:11">
+      <c r="A13" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="31">
+        <v>8001</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" s="20"/>
+      <c r="F13" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13" s="43">
+        <v>24094</v>
+      </c>
+      <c r="H13" s="44" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="20">
+        <v>18</v>
+      </c>
+      <c r="J13" s="24"/>
+      <c r="K13" s="38"/>
+    </row>
+    <row r="14" ht="14.25" spans="1:11">
+      <c r="A14" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="19">
+        <v>8002</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="H14" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" s="20">
+        <v>1</v>
+      </c>
+      <c r="J14" s="22"/>
+    </row>
+    <row r="15" ht="14.25" spans="1:11">
+      <c r="A15" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="19">
+        <v>8002</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="20"/>
+      <c r="F15" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" s="20">
+        <v>22682</v>
+      </c>
+      <c r="H15" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="20">
+        <v>32</v>
+      </c>
+      <c r="J15" s="27"/>
+      <c r="K15" s="28"/>
+    </row>
+    <row r="16" ht="14.25" spans="1:11">
+      <c r="A16" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="19">
+        <v>8002</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" s="20"/>
+      <c r="F16" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16" s="20">
+        <v>22279</v>
+      </c>
+      <c r="H16" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" s="20">
+        <v>1</v>
+      </c>
+      <c r="J16" s="22"/>
+    </row>
+    <row r="17" ht="14.25" spans="1:11">
+      <c r="A17" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="19">
+        <v>8002</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="20"/>
+      <c r="F17" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" s="20">
+        <v>22600</v>
+      </c>
+      <c r="H17" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="K7" s="10"/>
-      <c r="L7" s="6"/>
-    </row>
-    <row r="8" s="1" customFormat="1" ht="15" spans="1:12">
-      <c r="A8" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="33">
-        <v>8001</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="19">
-        <v>24006</v>
-      </c>
-      <c r="H8" s="50" t="s">
+      <c r="I17" s="20">
+        <v>1</v>
+      </c>
+      <c r="J17" s="42"/>
+    </row>
+    <row r="18" s="38" customFormat="1" ht="14.25" spans="1:11">
+      <c r="A18" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="19">
+        <v>8002</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" s="20"/>
+      <c r="F18" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G18" s="20">
+        <v>22601</v>
+      </c>
+      <c r="H18" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="I18" s="20">
+        <v>1</v>
+      </c>
+      <c r="J18" s="22"/>
+      <c r="K18" s="23"/>
+    </row>
+    <row r="19" s="38" customFormat="1" ht="14.25" spans="1:11">
+      <c r="A19" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="19">
+        <v>8002</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19" s="20"/>
+      <c r="F19" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G19" s="20">
+        <v>22602</v>
+      </c>
+      <c r="H19" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="I19" s="20">
+        <v>1</v>
+      </c>
+      <c r="J19" s="22"/>
+      <c r="K19" s="23"/>
+    </row>
+    <row r="20" ht="14.25" spans="1:11">
+      <c r="A20" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="19">
+        <v>8002</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="E20" s="20"/>
+      <c r="F20" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G20" s="20">
+        <v>22604</v>
+      </c>
+      <c r="H20" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="I8" s="6">
-        <v>1</v>
-      </c>
-      <c r="J8" s="11" t="s">
+      <c r="I20" s="20">
+        <v>1</v>
+      </c>
+      <c r="J20" s="22"/>
+    </row>
+    <row r="21" ht="14.25" spans="1:11">
+      <c r="A21" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="19">
+        <v>8002</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" s="20"/>
+      <c r="F21" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G21" s="20">
+        <v>22605</v>
+      </c>
+      <c r="H21" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="6"/>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="15" spans="1:12">
-      <c r="A9" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="33">
-        <v>8001</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" s="19">
-        <v>24007</v>
-      </c>
-      <c r="H9" s="50" t="s">
+      <c r="I21" s="20">
+        <v>1</v>
+      </c>
+      <c r="J21" s="22"/>
+    </row>
+    <row r="22" ht="14.25" spans="1:11">
+      <c r="A22" s="47" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="49">
+        <v>8002</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22" s="20"/>
+      <c r="F22" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="G22" s="20">
+        <v>22606</v>
+      </c>
+      <c r="H22" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="I22" s="20">
+        <v>1</v>
+      </c>
+      <c r="J22" s="51"/>
+      <c r="K22" s="52"/>
+    </row>
+    <row r="23" ht="14.25" spans="1:11">
+      <c r="A23" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" s="25">
+        <v>8002</v>
+      </c>
+      <c r="D23" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G23" s="25">
+        <v>22812</v>
+      </c>
+      <c r="H23" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="I23" s="25"/>
+      <c r="J23" s="22" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" ht="14.25" spans="1:11">
+      <c r="A24" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" s="25">
+        <v>8002</v>
+      </c>
+      <c r="D24" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G24" s="25">
+        <v>22814</v>
+      </c>
+      <c r="H24" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="I24" s="25"/>
+      <c r="J24" s="22" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25" spans="1:11">
+      <c r="A25" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" s="25">
+        <v>8002</v>
+      </c>
+      <c r="D25" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G25" s="25">
+        <v>22816</v>
+      </c>
+      <c r="H25" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="I25" s="25"/>
+      <c r="J25" s="22" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" ht="14.25" spans="1:11">
+      <c r="A26" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" s="19">
+        <v>8002</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="E26" s="20"/>
+      <c r="F26" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G26" s="20">
+        <v>22618</v>
+      </c>
+      <c r="H26" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="I26" s="20">
+        <v>1</v>
+      </c>
+      <c r="J26" s="22" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" ht="14.25" spans="1:11">
+      <c r="A27" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" s="19">
+        <v>8002</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="E27" s="20"/>
+      <c r="F27" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G27" s="20">
+        <v>22632</v>
+      </c>
+      <c r="H27" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="I27" s="20">
+        <v>1</v>
+      </c>
+      <c r="J27" s="22"/>
+    </row>
+    <row r="28" ht="14.25" spans="1:11">
+      <c r="A28" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" s="19">
+        <v>8002</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="E28" s="20"/>
+      <c r="F28" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G28" s="20">
+        <v>22634</v>
+      </c>
+      <c r="H28" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="I28" s="20">
+        <v>1</v>
+      </c>
+      <c r="J28" s="22"/>
+    </row>
+    <row r="29" ht="14.25" spans="1:11">
+      <c r="A29" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="19">
+        <v>8002</v>
+      </c>
+      <c r="D29" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="E29" s="20"/>
+      <c r="F29" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G29" s="20">
+        <v>22639</v>
+      </c>
+      <c r="H29" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="I9" s="6">
-        <v>1</v>
-      </c>
-      <c r="J9" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="K9" s="10"/>
-      <c r="L9" s="6"/>
-    </row>
-    <row r="10" ht="15" spans="1:12">
-      <c r="A10" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="35">
-        <v>8001</v>
-      </c>
-      <c r="D10" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="23"/>
-      <c r="F10" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G10" s="43">
-        <v>24008</v>
-      </c>
-      <c r="H10" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="I10" s="22"/>
-      <c r="J10" s="22"/>
-    </row>
-    <row r="11" ht="15" spans="1:12">
-      <c r="A11" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="35">
-        <v>8001</v>
-      </c>
-      <c r="D11" s="23" t="s">
+      <c r="I29" s="20">
+        <v>1</v>
+      </c>
+      <c r="J29" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="23"/>
-      <c r="F11" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" s="43">
-        <v>24009</v>
-      </c>
-      <c r="H11" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
-    </row>
-    <row r="12" ht="15" spans="1:12">
-      <c r="A12" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="35">
-        <v>8001</v>
-      </c>
-      <c r="D12" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E12" s="23"/>
-      <c r="F12" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G12" s="51">
-        <v>24012</v>
-      </c>
-      <c r="H12" s="24" t="s">
+    </row>
+    <row r="30" ht="14.25" spans="1:11">
+      <c r="A30" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" s="19">
+        <v>8002</v>
+      </c>
+      <c r="D30" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="E30" s="20"/>
+      <c r="F30" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G30" s="20">
+        <v>22642</v>
+      </c>
+      <c r="H30" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="I12" s="23">
-        <v>1</v>
-      </c>
-      <c r="J12" s="27" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" ht="15" spans="1:12">
-      <c r="A13" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="35">
-        <v>8001</v>
-      </c>
-      <c r="D13" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13" s="23"/>
-      <c r="F13" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G13" s="51">
-        <v>24016</v>
-      </c>
-      <c r="H13" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="I13" s="23">
-        <v>1</v>
-      </c>
-      <c r="J13" s="27"/>
-    </row>
-    <row r="14" ht="15" spans="1:12">
-      <c r="A14" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="35">
-        <v>8001</v>
-      </c>
-      <c r="D14" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="E14" s="23"/>
-      <c r="F14" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G14" s="51">
-        <v>24018</v>
-      </c>
-      <c r="H14" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="I14" s="23">
-        <v>1</v>
-      </c>
-      <c r="J14" s="27"/>
-    </row>
-    <row r="15" ht="15" spans="1:12">
-      <c r="A15" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="35">
-        <v>8001</v>
-      </c>
-      <c r="D15" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="E15" s="23"/>
-      <c r="F15" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G15" s="51">
-        <v>24032</v>
-      </c>
-      <c r="H15" s="24" t="s">
+      <c r="I30" s="20">
+        <v>1</v>
+      </c>
+      <c r="J30" s="22" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" ht="14.25" spans="1:11">
+      <c r="A31" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" s="19">
+        <v>8002</v>
+      </c>
+      <c r="D31" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="E31" s="20"/>
+      <c r="F31" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G31" s="20">
+        <v>22645</v>
+      </c>
+      <c r="H31" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="I15" s="23">
-        <v>1</v>
-      </c>
-      <c r="J15" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="L15" s="22">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="16" ht="15" spans="1:12">
-      <c r="A16" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="35">
-        <v>8001</v>
-      </c>
-      <c r="D16" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="E16" s="23"/>
-      <c r="F16" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G16" s="51">
-        <v>24035</v>
-      </c>
-      <c r="H16" s="24" t="s">
+      <c r="I31" s="20">
+        <v>1</v>
+      </c>
+      <c r="J31" s="22" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" ht="14.25" spans="1:11">
+      <c r="A32" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" s="39">
+        <v>8002</v>
+      </c>
+      <c r="D32" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="E32" s="20"/>
+      <c r="F32" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G32" s="39">
+        <v>22862</v>
+      </c>
+      <c r="H32" s="44" t="s">
+        <v>21</v>
+      </c>
+      <c r="I32" s="20">
+        <v>1</v>
+      </c>
+      <c r="J32" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="K32" s="53"/>
+    </row>
+    <row r="33" ht="14.25" spans="1:11">
+      <c r="A33" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C33" s="39">
+        <v>8002</v>
+      </c>
+      <c r="D33" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="E33" s="20"/>
+      <c r="F33" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G33" s="39">
+        <v>22864</v>
+      </c>
+      <c r="H33" s="44" t="s">
+        <v>21</v>
+      </c>
+      <c r="I33" s="20">
+        <v>1</v>
+      </c>
+      <c r="J33" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="K33" s="53"/>
+    </row>
+    <row r="34" ht="14.25" spans="1:11">
+      <c r="A34" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C34" s="39">
+        <v>8002</v>
+      </c>
+      <c r="D34" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="E34" s="20"/>
+      <c r="F34" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G34" s="39">
+        <v>22866</v>
+      </c>
+      <c r="H34" s="44" t="s">
+        <v>21</v>
+      </c>
+      <c r="I34" s="20">
+        <v>1</v>
+      </c>
+      <c r="J34" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="K34" s="53"/>
+    </row>
+    <row r="35" ht="14.25" spans="1:11">
+      <c r="A35" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C35" s="39">
+        <v>8002</v>
+      </c>
+      <c r="D35" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E35" s="20"/>
+      <c r="F35" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G35" s="39">
+        <v>22868</v>
+      </c>
+      <c r="H35" s="44" t="s">
+        <v>21</v>
+      </c>
+      <c r="I35" s="20">
+        <v>1</v>
+      </c>
+      <c r="J35" s="27" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="36" ht="14.25" spans="1:11">
+      <c r="A36" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C36" s="39">
+        <v>8002</v>
+      </c>
+      <c r="D36" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="E36" s="20"/>
+      <c r="F36" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G36" s="39">
+        <v>22870</v>
+      </c>
+      <c r="H36" s="44" t="s">
+        <v>21</v>
+      </c>
+      <c r="I36" s="20">
+        <v>1</v>
+      </c>
+      <c r="J36" s="27" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="37" ht="14.25" spans="1:11">
+      <c r="A37" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B37" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C37" s="39">
+        <v>8002</v>
+      </c>
+      <c r="D37" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="E37" s="20"/>
+      <c r="F37" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G37" s="39">
+        <v>22872</v>
+      </c>
+      <c r="H37" s="44" t="s">
+        <v>21</v>
+      </c>
+      <c r="I37" s="20">
+        <v>1</v>
+      </c>
+      <c r="J37" s="27" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="38" ht="14.25" spans="1:11">
+      <c r="A38" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B38" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C38" s="39">
+        <v>8002</v>
+      </c>
+      <c r="D38" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="E38" s="20"/>
+      <c r="F38" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G38" s="20">
+        <v>22276</v>
+      </c>
+      <c r="H38" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="23">
-        <v>1</v>
-      </c>
-      <c r="J16" s="27" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="17" ht="15" spans="1:12">
-      <c r="A17" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="B17" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="35">
-        <v>8001</v>
-      </c>
-      <c r="D17" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="F17" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G17" s="43">
-        <v>24039</v>
-      </c>
-      <c r="H17" s="24" t="s">
+      <c r="I38" s="20">
+        <v>1</v>
+      </c>
+      <c r="J38" s="22" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="39" ht="14.25" spans="1:11">
+      <c r="A39" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B39" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C39" s="39">
+        <v>8002</v>
+      </c>
+      <c r="D39" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="E39" s="20"/>
+      <c r="F39" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G39" s="20">
+        <v>22277</v>
+      </c>
+      <c r="H39" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="I17" s="23">
-        <v>1</v>
-      </c>
-      <c r="J17" s="27" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" s="42" customFormat="1" ht="15" spans="1:12">
-      <c r="A18" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="B18" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="35">
-        <v>8001</v>
-      </c>
-      <c r="D18" s="48" t="s">
-        <v>39</v>
-      </c>
-      <c r="E18" s="23"/>
-      <c r="F18" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="G18" s="52">
-        <v>24074</v>
-      </c>
-      <c r="H18" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="I18" s="23">
+      <c r="I39" s="20">
+        <v>1</v>
+      </c>
+      <c r="J39" s="22"/>
+    </row>
+    <row r="40" ht="14.25" spans="1:11">
+      <c r="A40" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B40" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C40" s="25">
+        <v>8002</v>
+      </c>
+      <c r="D40" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="E40" s="25"/>
+      <c r="F40" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G40" s="25">
+        <v>21856</v>
+      </c>
+      <c r="H40" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="I40" s="25">
+        <v>1</v>
+      </c>
+      <c r="J40" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="K40"/>
+    </row>
+    <row r="41" customFormat="1" ht="14.25" spans="1:11">
+      <c r="A41" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B41" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" s="25">
+        <v>8002</v>
+      </c>
+      <c r="D41" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="E41" s="25"/>
+      <c r="F41" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G41" s="25">
+        <v>22648</v>
+      </c>
+      <c r="H41" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="J18" s="27"/>
-      <c r="L18" s="54" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19" s="42" customFormat="1" ht="15" spans="1:12">
-      <c r="A19" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="B19" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="35">
-        <v>8001</v>
-      </c>
-      <c r="D19" s="48" t="s">
-        <v>41</v>
-      </c>
-      <c r="E19" s="23"/>
-      <c r="F19" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="G19" s="52">
-        <v>24094</v>
-      </c>
-      <c r="H19" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="I19" s="23">
+      <c r="I41" s="25">
+        <v>1</v>
+      </c>
+      <c r="J41" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="K41" s="23"/>
+    </row>
+    <row r="42" customFormat="1" ht="14.25" spans="1:11">
+      <c r="A42" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C42" s="25">
+        <v>8002</v>
+      </c>
+      <c r="D42" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="E42" s="25"/>
+      <c r="F42" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G42" s="25">
+        <v>22856</v>
+      </c>
+      <c r="H42" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="I42" s="25"/>
+      <c r="J42" s="25"/>
+    </row>
+    <row r="43" customFormat="1" ht="14.25" spans="1:11">
+      <c r="A43" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B43" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C43" s="25">
+        <v>8002</v>
+      </c>
+      <c r="D43" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="E43" s="25"/>
+      <c r="F43" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G43" s="25">
+        <v>22858</v>
+      </c>
+      <c r="H43" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="I43" s="25"/>
+      <c r="J43" s="25"/>
+    </row>
+    <row r="44" customFormat="1" ht="14.25" spans="1:11">
+      <c r="A44" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C44" s="25">
+        <v>8002</v>
+      </c>
+      <c r="D44" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="E44" s="25"/>
+      <c r="F44" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G44" s="25">
+        <v>22860</v>
+      </c>
+      <c r="H44" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="I44" s="25"/>
+      <c r="J44" s="25"/>
+    </row>
+    <row r="45" ht="14.25" spans="1:11">
+      <c r="A45" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B45" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C45" s="25">
+        <v>8002</v>
+      </c>
+      <c r="D45" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="E45" s="25"/>
+      <c r="F45" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G45" s="25">
+        <v>22874</v>
+      </c>
+      <c r="H45" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="J19" s="27"/>
-      <c r="L19" s="54" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20" ht="14.25" spans="1:12">
-      <c r="A20" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" s="22">
-        <v>8002</v>
-      </c>
-      <c r="D20" s="49" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G20" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="H20" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="I20" s="23">
-        <v>1</v>
-      </c>
-      <c r="J20" s="25"/>
-    </row>
-    <row r="21" ht="14.25" spans="1:12">
-      <c r="A21" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="B21" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" s="22">
-        <v>8002</v>
-      </c>
-      <c r="D21" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="E21" s="23"/>
-      <c r="F21" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="G21" s="55">
-        <v>22682</v>
-      </c>
-      <c r="H21" s="56" t="s">
-        <v>40</v>
-      </c>
-      <c r="I21" s="23">
-        <v>32</v>
-      </c>
-      <c r="J21" s="30"/>
-      <c r="K21" s="31"/>
-    </row>
-    <row r="22" ht="14.25" spans="1:12">
-      <c r="A22" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C22" s="22">
-        <v>8002</v>
-      </c>
-      <c r="D22" s="49" t="s">
-        <v>46</v>
-      </c>
-      <c r="E22" s="23"/>
-      <c r="F22" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G22" s="55">
-        <v>22279</v>
-      </c>
-      <c r="H22" s="24" t="s">
+      <c r="I45" s="25"/>
+      <c r="J45" s="25"/>
+    </row>
+    <row r="46" ht="14.25" spans="1:11">
+      <c r="A46" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B46" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C46" s="25">
+        <v>8002</v>
+      </c>
+      <c r="D46" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="E46" s="25"/>
+      <c r="F46" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G46" s="25">
+        <v>22875</v>
+      </c>
+      <c r="H46" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="I22" s="23">
-        <v>1</v>
-      </c>
-      <c r="J22" s="25"/>
-    </row>
-    <row r="23" ht="14.25" spans="1:12">
-      <c r="A23" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C23" s="22">
-        <v>8002</v>
-      </c>
-      <c r="D23" s="49" t="s">
-        <v>47</v>
-      </c>
-      <c r="E23" s="23"/>
-      <c r="F23" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G23" s="55">
-        <v>22600</v>
-      </c>
-      <c r="H23" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="I23" s="23">
-        <v>1</v>
-      </c>
-      <c r="J23" s="47"/>
-    </row>
-    <row r="24" ht="14.25" spans="1:12">
-      <c r="A24" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="B24" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C24" s="22">
-        <v>8002</v>
-      </c>
-      <c r="D24" s="49" t="s">
-        <v>48</v>
-      </c>
-      <c r="E24" s="23"/>
-      <c r="F24" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G24" s="55">
-        <v>22601</v>
-      </c>
-      <c r="H24" s="57" t="s">
-        <v>28</v>
-      </c>
-      <c r="I24" s="23">
-        <v>1</v>
-      </c>
-      <c r="J24" s="25"/>
-    </row>
-    <row r="25" ht="14.25" spans="1:12">
-      <c r="A25" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="B25" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25" s="22">
-        <v>8002</v>
-      </c>
-      <c r="D25" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="E25" s="23"/>
-      <c r="F25" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G25" s="55">
-        <v>22602</v>
-      </c>
-      <c r="H25" s="24" t="s">
+      <c r="I46" s="25"/>
+      <c r="J46" s="25"/>
+    </row>
+    <row r="47" ht="27.75" spans="1:11">
+      <c r="A47" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B47" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C47" s="25">
+        <v>8002</v>
+      </c>
+      <c r="D47" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="E47" s="25"/>
+      <c r="F47" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G47" s="25">
+        <v>22876</v>
+      </c>
+      <c r="H47" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="I47" s="25"/>
+      <c r="J47" s="25"/>
+    </row>
+    <row r="48" ht="27.75" spans="1:11">
+      <c r="A48" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C48" s="25">
+        <v>8002</v>
+      </c>
+      <c r="D48" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="E48" s="25"/>
+      <c r="F48" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G48" s="25">
+        <v>22877</v>
+      </c>
+      <c r="H48" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="I48" s="25"/>
+      <c r="J48" s="25"/>
+    </row>
+    <row r="49" ht="14.25" spans="1:10">
+      <c r="A49" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B49" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C49" s="25">
+        <v>8002</v>
+      </c>
+      <c r="D49" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="E49" s="25"/>
+      <c r="F49" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G49" s="25">
+        <v>22878</v>
+      </c>
+      <c r="H49" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="I49" s="25"/>
+      <c r="J49" s="25"/>
+    </row>
+    <row r="50" ht="14.25" spans="1:10">
+      <c r="A50" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B50" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C50" s="25">
+        <v>8002</v>
+      </c>
+      <c r="D50" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="E50" s="25"/>
+      <c r="F50" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G50" s="25">
+        <v>22879</v>
+      </c>
+      <c r="H50" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="I50" s="25"/>
+      <c r="J50" s="25"/>
+    </row>
+    <row r="51" ht="15" spans="1:10">
+      <c r="A51" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B51" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C51" s="25">
+        <v>8002</v>
+      </c>
+      <c r="D51" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="E51" s="25"/>
+      <c r="F51" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="G51" s="25">
+        <v>22902</v>
+      </c>
+      <c r="H51" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="I51" s="25"/>
+      <c r="J51" s="25"/>
+    </row>
+    <row r="52" ht="14.25" spans="1:10">
+      <c r="A52" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C52" s="25">
+        <v>8002</v>
+      </c>
+      <c r="D52" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="E52" s="25"/>
+      <c r="F52" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G52" s="25">
+        <v>22856</v>
+      </c>
+      <c r="H52" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="I25" s="23">
-        <v>1</v>
-      </c>
-      <c r="J25" s="25"/>
-    </row>
-    <row r="26" ht="14.25" spans="1:12">
-      <c r="A26" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="B26" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" s="22">
-        <v>8002</v>
-      </c>
-      <c r="D26" s="49" t="s">
-        <v>50</v>
-      </c>
-      <c r="E26" s="23"/>
-      <c r="F26" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G26" s="55">
-        <v>22604</v>
-      </c>
-      <c r="H26" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="I26" s="23">
-        <v>1</v>
-      </c>
-      <c r="J26" s="25"/>
-    </row>
-    <row r="27" ht="14.25" spans="1:12">
-      <c r="A27" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="B27" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C27" s="22">
-        <v>8002</v>
-      </c>
-      <c r="D27" s="49" t="s">
-        <v>51</v>
-      </c>
-      <c r="E27" s="23"/>
-      <c r="F27" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G27" s="55">
-        <v>22605</v>
-      </c>
-      <c r="H27" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="I27" s="23">
-        <v>1</v>
-      </c>
-      <c r="J27" s="25"/>
-    </row>
-    <row r="28" ht="14.25" spans="1:12">
-      <c r="A28" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="B28" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C28" s="22">
-        <v>8002</v>
-      </c>
-      <c r="D28" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="E28" s="23"/>
-      <c r="F28" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G28" s="55">
-        <v>22606</v>
-      </c>
-      <c r="H28" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="I28" s="23">
-        <v>1</v>
-      </c>
-      <c r="J28" s="25"/>
-    </row>
-    <row r="29" ht="14.25" spans="1:12">
-      <c r="A29" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="B29" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C29" s="22">
-        <v>8002</v>
-      </c>
-      <c r="D29" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="E29" s="23"/>
-      <c r="F29" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G29" s="55">
-        <v>22612</v>
-      </c>
-      <c r="H29" s="24" t="s">
+      <c r="I52" s="25"/>
+      <c r="J52" s="25"/>
+    </row>
+    <row r="53" ht="14.25" spans="1:10">
+      <c r="A53" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B53" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C53" s="25">
+        <v>8002</v>
+      </c>
+      <c r="D53" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E53" s="25"/>
+      <c r="F53" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G53" s="25">
+        <v>22858</v>
+      </c>
+      <c r="H53" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="23">
-        <v>1</v>
-      </c>
-      <c r="J29" s="25" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="30" ht="14.25" spans="1:12">
-      <c r="A30" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C30" s="22">
-        <v>8002</v>
-      </c>
-      <c r="D30" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="E30" s="23"/>
-      <c r="F30" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G30" s="55">
-        <v>22614</v>
-      </c>
-      <c r="H30" s="24" t="s">
+      <c r="I53" s="25"/>
+      <c r="J53" s="25"/>
+    </row>
+    <row r="54" ht="14.25" spans="1:10">
+      <c r="A54" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B54" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C54" s="25">
+        <v>8002</v>
+      </c>
+      <c r="D54" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="E54" s="25"/>
+      <c r="F54" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G54" s="25">
+        <v>22860</v>
+      </c>
+      <c r="H54" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="I30" s="23">
-        <v>1</v>
-      </c>
-      <c r="J30" s="25" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="31" ht="14.25" spans="1:12">
-      <c r="A31" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="B31" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C31" s="22">
-        <v>8002</v>
-      </c>
-      <c r="D31" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="E31" s="23"/>
-      <c r="F31" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G31" s="55">
-        <v>22616</v>
-      </c>
-      <c r="H31" s="24" t="s">
+      <c r="I54" s="25"/>
+      <c r="J54" s="25"/>
+    </row>
+    <row r="55" ht="14.25" spans="1:10">
+      <c r="A55" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B55" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C55" s="25">
+        <v>8002</v>
+      </c>
+      <c r="D55" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="E55" s="25"/>
+      <c r="F55" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G55" s="25">
+        <v>22818</v>
+      </c>
+      <c r="H55" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="I31" s="23">
-        <v>1</v>
-      </c>
-      <c r="J31" s="25" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="32" ht="14.25" spans="1:12">
-      <c r="A32" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="B32" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C32" s="22">
-        <v>8002</v>
-      </c>
-      <c r="D32" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="E32" s="23"/>
-      <c r="F32" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G32" s="55">
-        <v>22618</v>
-      </c>
-      <c r="H32" s="24" t="s">
+      <c r="I55" s="25"/>
+      <c r="J55" s="25"/>
+    </row>
+    <row r="56" ht="14.25" spans="1:10">
+      <c r="A56" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B56" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C56" s="25">
+        <v>8002</v>
+      </c>
+      <c r="D56" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="E56" s="25"/>
+      <c r="F56" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G56" s="25">
+        <v>22854</v>
+      </c>
+      <c r="H56" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="I32" s="23">
-        <v>1</v>
-      </c>
-      <c r="J32" s="25" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="33" ht="14.25" spans="1:12">
-      <c r="A33" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C33" s="22">
-        <v>8002</v>
-      </c>
-      <c r="D33" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="E33" s="23"/>
-      <c r="F33" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G33" s="55">
-        <v>22632</v>
-      </c>
-      <c r="H33" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="I33" s="23">
-        <v>1</v>
-      </c>
-      <c r="J33" s="25"/>
-    </row>
-    <row r="34" ht="14.25" spans="1:12">
-      <c r="A34" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="B34" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C34" s="22">
-        <v>8002</v>
-      </c>
-      <c r="D34" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="E34" s="23"/>
-      <c r="F34" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G34" s="55">
-        <v>22634</v>
-      </c>
-      <c r="H34" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="I34" s="23">
-        <v>1</v>
-      </c>
-      <c r="J34" s="25"/>
-    </row>
-    <row r="35" ht="14.25" spans="1:12">
-      <c r="A35" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C35" s="22">
-        <v>8002</v>
-      </c>
-      <c r="D35" s="49" t="s">
-        <v>60</v>
-      </c>
-      <c r="E35" s="23"/>
-      <c r="F35" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G35" s="55">
-        <v>22639</v>
-      </c>
-      <c r="H35" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="I35" s="23">
-        <v>1</v>
-      </c>
-      <c r="J35" s="25" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="36" ht="14.25" spans="1:12">
-      <c r="A36" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C36" s="22">
-        <v>8002</v>
-      </c>
-      <c r="D36" s="49" t="s">
-        <v>61</v>
-      </c>
-      <c r="E36" s="23"/>
-      <c r="F36" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G36" s="55">
-        <v>22642</v>
-      </c>
-      <c r="H36" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="I36" s="23">
-        <v>1</v>
-      </c>
-      <c r="J36" s="25" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="37" ht="14.25" spans="1:12">
-      <c r="A37" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="B37" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C37" s="22">
-        <v>8002</v>
-      </c>
-      <c r="D37" s="49" t="s">
-        <v>62</v>
-      </c>
-      <c r="E37" s="23"/>
-      <c r="F37" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G37" s="55">
-        <v>22645</v>
-      </c>
-      <c r="H37" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="I37" s="23">
-        <v>1</v>
-      </c>
-      <c r="J37" s="25" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="38" ht="14.25" spans="1:12">
-      <c r="A38" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="B38" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C38" s="22">
-        <v>8002</v>
-      </c>
-      <c r="D38" s="49" t="s">
-        <v>63</v>
-      </c>
-      <c r="E38" s="23"/>
-      <c r="F38" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G38" s="55">
-        <v>22660</v>
-      </c>
-      <c r="H38" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="I38" s="23">
-        <v>1</v>
-      </c>
-      <c r="J38" s="25" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="39" ht="14.25" spans="1:12">
-      <c r="A39" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="B39" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C39" s="22">
-        <v>8002</v>
-      </c>
-      <c r="D39" s="49" t="s">
-        <v>64</v>
-      </c>
-      <c r="E39" s="23"/>
-      <c r="F39" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G39" s="55">
-        <v>22662</v>
-      </c>
-      <c r="H39" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="I39" s="23">
-        <v>1</v>
-      </c>
-      <c r="J39" s="25" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="40" ht="14.25" spans="1:12">
-      <c r="A40" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C40" s="22">
-        <v>8002</v>
-      </c>
-      <c r="D40" s="49" t="s">
-        <v>66</v>
-      </c>
-      <c r="E40" s="23"/>
-      <c r="F40" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G40" s="55">
-        <v>22664</v>
-      </c>
-      <c r="H40" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="I40" s="23">
-        <v>1</v>
-      </c>
-      <c r="J40" s="25" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="41" customFormat="1" ht="14.25" spans="1:12">
-      <c r="A41" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C41" s="22">
-        <v>8002</v>
-      </c>
-      <c r="D41" s="49" t="s">
-        <v>67</v>
-      </c>
-      <c r="E41" s="23"/>
-      <c r="F41" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G41" s="55">
-        <v>22276</v>
-      </c>
-      <c r="H41" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="I41" s="23">
-        <v>1</v>
-      </c>
-      <c r="J41" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="K41" s="26"/>
-      <c r="L41" s="22"/>
-    </row>
-    <row r="42" customFormat="1" ht="14.25" spans="1:12">
-      <c r="A42" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C42" s="22">
-        <v>8002</v>
-      </c>
-      <c r="D42" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="E42" s="23"/>
-      <c r="F42" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G42" s="55">
-        <v>22277</v>
-      </c>
-      <c r="H42" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="I42" s="23">
-        <v>1</v>
-      </c>
-      <c r="J42" s="25"/>
-      <c r="K42" s="26"/>
-      <c r="L42" s="22"/>
-    </row>
-    <row r="43" customFormat="1" ht="14.25" spans="1:12">
-      <c r="A43" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="B43" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C43" s="22">
-        <v>8002</v>
-      </c>
-      <c r="D43" s="49" t="s">
-        <v>69</v>
-      </c>
-      <c r="E43" s="23"/>
-      <c r="F43" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G43" s="55">
-        <v>21856</v>
-      </c>
-      <c r="H43" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="I43" s="23">
-        <v>1</v>
-      </c>
-      <c r="J43" s="25" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="44" customFormat="1" ht="14.25" spans="1:12">
-      <c r="A44" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="B44" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C44" s="22">
-        <v>9004</v>
-      </c>
-      <c r="D44" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="E44" s="23"/>
-      <c r="F44" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G44" s="23">
-        <v>22648</v>
-      </c>
-      <c r="H44" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="I44" s="23">
-        <v>1</v>
-      </c>
-      <c r="J44" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="K44" s="26"/>
-      <c r="L44" s="22"/>
+      <c r="I56" s="25"/>
+      <c r="J56" s="25"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O44" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:N56" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
-  <conditionalFormatting sqref="D18">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D19">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D43">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D44">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D41:D42">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D1 D3:D6 D8:D17 D20:D40 D45:D1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -2873,16 +3174,16 @@
     <row r="1" ht="14.25"/>
     <row r="2" s="1" customFormat="1" ht="14.25" spans="1:12">
       <c r="A2" s="4" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C2" s="6">
         <v>9004</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="E2" s="7"/>
       <c r="F2" s="4" t="s">
@@ -2890,7 +3191,7 @@
       </c>
       <c r="G2" s="7"/>
       <c r="H2" s="8" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="I2" s="7">
         <v>1</v>
@@ -2901,16 +3202,16 @@
     </row>
     <row r="3" s="1" customFormat="1" ht="14.25" spans="1:12">
       <c r="A3" s="4" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C3" s="6">
         <v>9004</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="E3" s="7"/>
       <c r="F3" s="4" t="s">
@@ -2918,7 +3219,7 @@
       </c>
       <c r="G3" s="7"/>
       <c r="H3" s="8" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="I3" s="7">
         <v>1</v>
@@ -2929,277 +3230,277 @@
     </row>
     <row r="4" s="2" customFormat="1" ht="14.25" spans="1:12">
       <c r="A4" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" s="14">
+        <v>83</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="13">
         <v>9004</v>
       </c>
-      <c r="D4" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="E4" s="15"/>
+      <c r="D4" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E4" s="7"/>
       <c r="F4" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="14"/>
-      <c r="H4" s="16" t="s">
+      <c r="G4" s="13"/>
+      <c r="H4" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="15">
-        <v>1</v>
-      </c>
-      <c r="J4" s="17"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="19"/>
+      <c r="I4" s="7">
+        <v>1</v>
+      </c>
+      <c r="J4" s="15"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="13"/>
     </row>
     <row r="5" customFormat="1" ht="14.25" hidden="1"/>
     <row r="6" ht="14.25" spans="1:12">
-      <c r="A6" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="22">
+      <c r="A6" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="19">
         <v>9004</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E6" s="23"/>
-      <c r="F6" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="23"/>
-      <c r="H6" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="I6" s="23">
-        <v>1</v>
-      </c>
-      <c r="J6" s="25"/>
-      <c r="K6" s="26"/>
-      <c r="L6" s="22"/>
+        <v>87</v>
+      </c>
+      <c r="E6" s="20"/>
+      <c r="F6" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="20"/>
+      <c r="H6" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="I6" s="20">
+        <v>1</v>
+      </c>
+      <c r="J6" s="22"/>
+      <c r="K6" s="23"/>
+      <c r="L6" s="19"/>
     </row>
     <row r="7" ht="14.25" spans="1:12">
-      <c r="A7" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="B7" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" s="22">
+      <c r="A7" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="19">
         <v>9004</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E7" s="23"/>
-      <c r="F7" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" s="23"/>
-      <c r="H7" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="I7" s="23">
-        <v>1</v>
-      </c>
-      <c r="J7" s="25"/>
-      <c r="K7" s="26"/>
-      <c r="L7" s="22"/>
+        <v>88</v>
+      </c>
+      <c r="E7" s="20"/>
+      <c r="F7" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="20"/>
+      <c r="H7" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="I7" s="20">
+        <v>1</v>
+      </c>
+      <c r="J7" s="22"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="19"/>
     </row>
     <row r="8" ht="14.25" spans="1:12">
-      <c r="A8" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="B8" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" s="22">
+      <c r="A8" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="19">
         <v>9004</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="E8" s="23"/>
-      <c r="F8" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="23"/>
-      <c r="H8" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="E8" s="20"/>
+      <c r="F8" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="20"/>
+      <c r="H8" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="I8" s="23">
-        <v>1</v>
-      </c>
-      <c r="J8" s="25"/>
-      <c r="K8" s="26"/>
-      <c r="L8" s="22"/>
+      <c r="I8" s="20">
+        <v>1</v>
+      </c>
+      <c r="J8" s="22"/>
+      <c r="K8" s="23"/>
+      <c r="L8" s="19"/>
     </row>
     <row r="9" ht="14.25" spans="1:12">
-      <c r="A9" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="B9" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" s="22">
+      <c r="A9" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="19">
         <v>9004</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="E9" s="23"/>
-      <c r="F9" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" s="23"/>
-      <c r="H9" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="E9" s="20"/>
+      <c r="F9" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" s="20"/>
+      <c r="H9" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="I9" s="23">
-        <v>1</v>
-      </c>
-      <c r="J9" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="K9" s="26"/>
-      <c r="L9" s="22"/>
+      <c r="I9" s="20">
+        <v>1</v>
+      </c>
+      <c r="J9" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="K9" s="23"/>
+      <c r="L9" s="19"/>
     </row>
     <row r="10" ht="14.25" spans="1:12">
-      <c r="A10" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="B10" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" s="22">
+      <c r="A10" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="19">
         <v>9004</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="E10" s="23"/>
-      <c r="F10" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G10" s="23"/>
-      <c r="H10" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="E10" s="20"/>
+      <c r="F10" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" s="20"/>
+      <c r="H10" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="I10" s="23">
-        <v>1</v>
-      </c>
-      <c r="J10" s="25" t="s">
-        <v>65</v>
-      </c>
-      <c r="K10" s="26"/>
-      <c r="L10" s="22"/>
+      <c r="I10" s="20">
+        <v>1</v>
+      </c>
+      <c r="J10" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="K10" s="23"/>
+      <c r="L10" s="19"/>
     </row>
     <row r="11" ht="14.25" spans="1:12">
-      <c r="A11" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="B11" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" s="22">
+      <c r="A11" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="19">
         <v>9004</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="E11" s="23"/>
-      <c r="F11" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" s="23"/>
-      <c r="H11" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="E11" s="20"/>
+      <c r="F11" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="20"/>
+      <c r="H11" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="I11" s="23">
-        <v>1</v>
-      </c>
-      <c r="J11" s="25" t="s">
-        <v>65</v>
-      </c>
-      <c r="K11" s="26"/>
-      <c r="L11" s="22"/>
+      <c r="I11" s="20">
+        <v>1</v>
+      </c>
+      <c r="J11" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="K11" s="23"/>
+      <c r="L11" s="19"/>
     </row>
     <row r="12" ht="14.25" spans="1:12">
-      <c r="A12" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="B12" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C12" s="22">
+      <c r="A12" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="19">
         <v>9004</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E12" s="23"/>
-      <c r="F12" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G12" s="23"/>
-      <c r="H12" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="E12" s="20"/>
+      <c r="F12" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" s="20"/>
+      <c r="H12" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="I12" s="23">
-        <v>1</v>
-      </c>
-      <c r="J12" s="25" t="s">
-        <v>65</v>
-      </c>
-      <c r="K12" s="26"/>
-      <c r="L12" s="22"/>
+      <c r="I12" s="20">
+        <v>1</v>
+      </c>
+      <c r="J12" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="K12" s="23"/>
+      <c r="L12" s="19"/>
     </row>
     <row r="13" ht="14.25" spans="1:12">
-      <c r="A13" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="B13" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C13" s="22">
+      <c r="A13" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="19">
         <v>9004</v>
       </c>
-      <c r="D13" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="E13" s="23"/>
-      <c r="F13" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="G13" s="27"/>
-      <c r="H13" s="29" t="s">
+      <c r="D13" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="E13" s="20"/>
+      <c r="F13" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="G13" s="24"/>
+      <c r="H13" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="21">
-        <v>1</v>
-      </c>
-      <c r="J13" s="30"/>
-      <c r="K13" s="31"/>
-      <c r="L13" s="22"/>
+      <c r="I13" s="18">
+        <v>1</v>
+      </c>
+      <c r="J13" s="27"/>
+      <c r="K13" s="28"/>
+      <c r="L13" s="19"/>
     </row>
     <row r="14" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
-      <c r="A14" s="32" t="s">
-        <v>84</v>
+      <c r="A14" s="12" t="s">
+        <v>96</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="33">
+      <c r="C14" s="29">
         <v>8001</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
@@ -3210,17 +3511,17 @@
       <c r="L14" s="6"/>
     </row>
     <row r="15" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
-      <c r="A15" s="32" t="s">
-        <v>84</v>
+      <c r="A15" s="12" t="s">
+        <v>96</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="33">
+      <c r="C15" s="29">
         <v>8001</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
@@ -3231,17 +3532,17 @@
       <c r="L15" s="6"/>
     </row>
     <row r="16" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
-      <c r="A16" s="32" t="s">
-        <v>84</v>
+      <c r="A16" s="12" t="s">
+        <v>96</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="33">
+      <c r="C16" s="29">
         <v>8001</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
@@ -3252,17 +3553,17 @@
       <c r="L16" s="6"/>
     </row>
     <row r="17" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
-      <c r="A17" s="32" t="s">
-        <v>84</v>
+      <c r="A17" s="12" t="s">
+        <v>96</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="33">
+      <c r="C17" s="29">
         <v>8001</v>
       </c>
-      <c r="D17" s="34" t="s">
-        <v>88</v>
+      <c r="D17" s="30" t="s">
+        <v>100</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
@@ -3273,17 +3574,17 @@
       <c r="L17" s="6"/>
     </row>
     <row r="18" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
-      <c r="A18" s="32" t="s">
-        <v>84</v>
+      <c r="A18" s="12" t="s">
+        <v>96</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="33">
+      <c r="C18" s="29">
         <v>8001</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
@@ -3294,17 +3595,17 @@
       <c r="L18" s="6"/>
     </row>
     <row r="19" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
-      <c r="A19" s="32" t="s">
-        <v>84</v>
+      <c r="A19" s="12" t="s">
+        <v>96</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="33">
+      <c r="C19" s="29">
         <v>8001</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
@@ -3315,17 +3616,17 @@
       <c r="L19" s="6"/>
     </row>
     <row r="20" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
-      <c r="A20" s="32" t="s">
-        <v>84</v>
+      <c r="A20" s="12" t="s">
+        <v>96</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="33">
+      <c r="C20" s="29">
         <v>8001</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
@@ -3336,17 +3637,17 @@
       <c r="L20" s="6"/>
     </row>
     <row r="21" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
-      <c r="A21" s="32" t="s">
-        <v>84</v>
+      <c r="A21" s="12" t="s">
+        <v>96</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="33">
+      <c r="C21" s="29">
         <v>8001</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
@@ -3357,17 +3658,17 @@
       <c r="L21" s="6"/>
     </row>
     <row r="22" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
-      <c r="A22" s="32" t="s">
-        <v>84</v>
+      <c r="A22" s="12" t="s">
+        <v>96</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="33">
+      <c r="C22" s="29">
         <v>8001</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
@@ -3378,17 +3679,17 @@
       <c r="L22" s="6"/>
     </row>
     <row r="23" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
-      <c r="A23" s="32" t="s">
-        <v>84</v>
+      <c r="A23" s="12" t="s">
+        <v>96</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="33">
+      <c r="C23" s="29">
         <v>8001</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
@@ -3399,17 +3700,17 @@
       <c r="L23" s="6"/>
     </row>
     <row r="24" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
-      <c r="A24" s="32" t="s">
-        <v>84</v>
+      <c r="A24" s="12" t="s">
+        <v>96</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="33">
+      <c r="C24" s="29">
         <v>8001</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
@@ -3420,67 +3721,67 @@
       <c r="L24" s="6"/>
     </row>
     <row r="25" ht="15" hidden="1" spans="1:12">
-      <c r="A25" s="28" t="s">
-        <v>84</v>
-      </c>
-      <c r="B25" s="21" t="s">
+      <c r="A25" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C25" s="35">
+      <c r="C25" s="31">
         <v>8001</v>
       </c>
-      <c r="D25" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="F25" s="21" t="s">
+      <c r="D25" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="F25" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="G25" s="24"/>
+      <c r="H25" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="I25" s="18">
+        <v>1</v>
+      </c>
+      <c r="J25" s="19"/>
+      <c r="K25" s="23"/>
+      <c r="L25" s="19"/>
+    </row>
+    <row r="26" s="3" customFormat="1" ht="14.25" spans="1:12">
+      <c r="A26" s="32" t="s">
         <v>83</v>
       </c>
-      <c r="G25" s="27"/>
-      <c r="H25" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="I25" s="21">
-        <v>1</v>
-      </c>
-      <c r="J25" s="22"/>
-      <c r="K25" s="26"/>
-      <c r="L25" s="22"/>
-    </row>
-    <row r="26" s="3" customFormat="1" ht="14.25" spans="1:12">
-      <c r="A26" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="B26" s="37" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" s="38">
+      <c r="B26" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" s="34">
         <v>9004</v>
       </c>
-      <c r="D26" s="39" t="s">
-        <v>96</v>
-      </c>
-      <c r="E26" s="39"/>
-      <c r="F26" s="36" t="s">
-        <v>17</v>
-      </c>
-      <c r="G26" s="39"/>
-      <c r="H26" s="40" t="s">
+      <c r="D26" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="E26" s="35"/>
+      <c r="F26" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="G26" s="35"/>
+      <c r="H26" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="I26" s="39">
-        <v>1</v>
-      </c>
-      <c r="J26" s="41" t="s">
-        <v>65</v>
+      <c r="I26" s="35">
+        <v>1</v>
+      </c>
+      <c r="J26" s="37" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:D26" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="0">
-      <filters>
-        <filter val="B线"/>
-        <filter val="六分厂6-1装配B线"/>
-      </filters>
+      <customFilters>
+        <customFilter operator="equal" val="B线"/>
+        <customFilter operator="equal" val="六分厂6-1装配B线"/>
+      </customFilters>
     </filterColumn>
     <extLst/>
   </autoFilter>

--- a/doc/六分厂6-1#装配线/点位信息.xlsx
+++ b/doc/六分厂6-1#装配线/点位信息.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Sheet3" sheetId="7" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$3:$D$26</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="97">
   <si>
     <t>设备名称</t>
   </si>
@@ -143,15 +143,12 @@
     <t>100.100.100.6</t>
   </si>
   <si>
-    <t>58D</t>
+    <t>58E</t>
   </si>
   <si>
     <t>序列码</t>
   </si>
   <si>
-    <t>ABS检测齿数</t>
-  </si>
-  <si>
     <t>托盘号B</t>
   </si>
   <si>
@@ -188,106 +185,73 @@
     <t>密封圈压装压力</t>
   </si>
   <si>
+    <t>({0}/10000)</t>
+  </si>
+  <si>
+    <t>密封圈压装位移B</t>
+  </si>
+  <si>
+    <t>磁性圈平行差检测传感器1</t>
+  </si>
+  <si>
+    <t>磁性圈平行差检测传感器2</t>
+  </si>
+  <si>
+    <t>磁性圈平行差检测传感器3</t>
+  </si>
+  <si>
+    <t>磁性圈平行差平均值</t>
+  </si>
+  <si>
+    <t>端跳值轴</t>
+  </si>
+  <si>
+    <t>端跳值平面</t>
+  </si>
+  <si>
+    <t>端跳值高度</t>
+  </si>
+  <si>
+    <t>1400 TQ</t>
+  </si>
+  <si>
+    <t>1400 M/HIGH</t>
+  </si>
+  <si>
+    <t>1600 P/M1400=ABSSINGLE MAX</t>
+  </si>
+  <si>
+    <t>1600 P/M1400=ABSSINGLE min</t>
+  </si>
+  <si>
+    <t>1600 P/M1400=ABSTOTAL</t>
+  </si>
+  <si>
+    <t>1600 P/M1400=ABSTOOTH</t>
+  </si>
+  <si>
+    <t>震动检测结果</t>
+  </si>
+  <si>
+    <t>跳动检测值</t>
+  </si>
+  <si>
+    <t>扁平度</t>
+  </si>
+  <si>
+    <t>实测间隙</t>
+  </si>
+  <si>
+    <t>1150 GONO CHECK</t>
+  </si>
+  <si>
+    <t>B线</t>
+  </si>
+  <si>
+    <t>防尘盖压装压力</t>
+  </si>
+  <si>
     <t>Single</t>
-  </si>
-  <si>
-    <t>密封圈压装位移B</t>
-  </si>
-  <si>
-    <t>磁性圈平行差检测传感器1</t>
-  </si>
-  <si>
-    <t>磁性圈平行差检测传感器2</t>
-  </si>
-  <si>
-    <t>磁性圈平行差检测传感器3</t>
-  </si>
-  <si>
-    <t>振动下LOAD</t>
-  </si>
-  <si>
-    <t>({0}/10)</t>
-  </si>
-  <si>
-    <t>振动下LH</t>
-  </si>
-  <si>
-    <t>({0}/10000)</t>
-  </si>
-  <si>
-    <t>振动下RH</t>
-  </si>
-  <si>
-    <t>振动上LOAD</t>
-  </si>
-  <si>
-    <t>振动上LH</t>
-  </si>
-  <si>
-    <t>振动上RH</t>
-  </si>
-  <si>
-    <t>ABS检测峰值</t>
-  </si>
-  <si>
-    <t>ABS检测谷值</t>
-  </si>
-  <si>
-    <t>径跳值</t>
-  </si>
-  <si>
-    <t>磁性圈平行差</t>
-  </si>
-  <si>
-    <t>端跳值轴</t>
-  </si>
-  <si>
-    <t>端跳值平面</t>
-  </si>
-  <si>
-    <t>端跳值高度</t>
-  </si>
-  <si>
-    <t>1400 TQ</t>
-  </si>
-  <si>
-    <t>1400 M/HIGH</t>
-  </si>
-  <si>
-    <t>1600 P/M1400=ABSSINGLE MAX</t>
-  </si>
-  <si>
-    <t>1600 P/M1400=ABSSINGLE min</t>
-  </si>
-  <si>
-    <t>1600 P/M1400=ABSTOTAL</t>
-  </si>
-  <si>
-    <t>1600 P/M1400=ABSTOOTH</t>
-  </si>
-  <si>
-    <t>震动检测结果</t>
-  </si>
-  <si>
-    <t>跳动检测值</t>
-  </si>
-  <si>
-    <t>扁平度</t>
-  </si>
-  <si>
-    <t>高度上限</t>
-  </si>
-  <si>
-    <t>实测间隙</t>
-  </si>
-  <si>
-    <t>1150 GONO CHECK</t>
-  </si>
-  <si>
-    <t>B线</t>
-  </si>
-  <si>
-    <t>防尘盖压装压力</t>
   </si>
   <si>
     <t>防尘盖压装位移</t>
@@ -1226,11 +1190,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1551,8 +1515,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:K56"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1604,7 +1568,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" ht="15" spans="1:11">
+    <row r="2" ht="14.25" hidden="1" spans="1:11">
       <c r="A2" s="25" t="s">
         <v>11</v>
       </c>
@@ -1631,7 +1595,7 @@
       </c>
       <c r="J2" s="19"/>
     </row>
-    <row r="3" ht="15" spans="1:11">
+    <row r="3" ht="15" hidden="1" spans="1:11">
       <c r="A3" s="25" t="s">
         <v>11</v>
       </c>
@@ -1658,7 +1622,7 @@
       </c>
       <c r="J3" s="19"/>
     </row>
-    <row r="4" ht="15" spans="1:11">
+    <row r="4" ht="15" hidden="1" spans="1:11">
       <c r="A4" s="25" t="s">
         <v>11</v>
       </c>
@@ -1685,7 +1649,7 @@
       </c>
       <c r="J4" s="19"/>
     </row>
-    <row r="5" ht="15" spans="1:11">
+    <row r="5" ht="15" hidden="1" spans="1:11">
       <c r="A5" s="25" t="s">
         <v>11</v>
       </c>
@@ -1712,7 +1676,7 @@
       </c>
       <c r="J5" s="19"/>
     </row>
-    <row r="6" ht="15" spans="1:11">
+    <row r="6" ht="15" hidden="1" spans="1:11">
       <c r="A6" s="25" t="s">
         <v>11</v>
       </c>
@@ -1739,7 +1703,7 @@
       </c>
       <c r="J6" s="19"/>
     </row>
-    <row r="7" s="1" customFormat="1" ht="15" spans="1:11">
+    <row r="7" s="1" customFormat="1" ht="15" hidden="1" spans="1:11">
       <c r="A7" s="25" t="s">
         <v>11</v>
       </c>
@@ -1766,7 +1730,7 @@
       <c r="J7" s="19"/>
       <c r="K7" s="23"/>
     </row>
-    <row r="8" s="1" customFormat="1" ht="15" spans="1:11">
+    <row r="8" s="1" customFormat="1" ht="15" hidden="1" spans="1:11">
       <c r="A8" s="25" t="s">
         <v>11</v>
       </c>
@@ -1793,7 +1757,7 @@
       <c r="J8" s="19"/>
       <c r="K8" s="23"/>
     </row>
-    <row r="9" s="1" customFormat="1" ht="15" spans="1:11">
+    <row r="9" s="1" customFormat="1" ht="15" hidden="1" spans="1:11">
       <c r="A9" s="25" t="s">
         <v>11</v>
       </c>
@@ -1824,7 +1788,7 @@
       </c>
       <c r="K9" s="23"/>
     </row>
-    <row r="10" ht="15" spans="1:11">
+    <row r="10" ht="15" hidden="1" spans="1:11">
       <c r="A10" s="25" t="s">
         <v>11</v>
       </c>
@@ -1854,7 +1818,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" ht="15" spans="1:11">
+    <row r="11" ht="15" hidden="1" spans="1:11">
       <c r="A11" s="25" t="s">
         <v>11</v>
       </c>
@@ -1883,7 +1847,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" ht="15" spans="1:11">
+    <row r="12" ht="15" hidden="1" spans="1:11">
       <c r="A12" s="25" t="s">
         <v>11</v>
       </c>
@@ -1912,7 +1876,7 @@
       <c r="J12" s="24"/>
       <c r="K12" s="38"/>
     </row>
-    <row r="13" ht="15" spans="1:11">
+    <row r="13" ht="15" hidden="1" spans="1:11">
       <c r="A13" s="25" t="s">
         <v>11</v>
       </c>
@@ -1969,7 +1933,7 @@
       </c>
       <c r="J14" s="22"/>
     </row>
-    <row r="15" ht="14.25" spans="1:11">
+    <row r="15" spans="1:11">
       <c r="A15" s="25" t="s">
         <v>34</v>
       </c>
@@ -1987,7 +1951,7 @@
         <v>17</v>
       </c>
       <c r="G15" s="20">
-        <v>22682</v>
+        <v>22882</v>
       </c>
       <c r="H15" s="45" t="s">
         <v>32</v>
@@ -2002,7 +1966,7 @@
       <c r="A16" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="24" t="s">
         <v>35</v>
       </c>
       <c r="C16" s="19">
@@ -2016,21 +1980,21 @@
         <v>17</v>
       </c>
       <c r="G16" s="20">
-        <v>22279</v>
+        <v>22800</v>
       </c>
       <c r="H16" s="21" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I16" s="20">
         <v>1</v>
       </c>
-      <c r="J16" s="22"/>
-    </row>
-    <row r="17" ht="14.25" spans="1:11">
+      <c r="J16" s="42"/>
+    </row>
+    <row r="17" s="38" customFormat="1" ht="14.25" spans="1:11">
       <c r="A17" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="24" t="s">
+      <c r="B17" s="18" t="s">
         <v>35</v>
       </c>
       <c r="C17" s="19">
@@ -2044,21 +2008,22 @@
         <v>17</v>
       </c>
       <c r="G17" s="20">
-        <v>22600</v>
-      </c>
-      <c r="H17" s="21" t="s">
+        <v>22801</v>
+      </c>
+      <c r="H17" s="46" t="s">
         <v>24</v>
       </c>
       <c r="I17" s="20">
         <v>1</v>
       </c>
-      <c r="J17" s="42"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="23"/>
     </row>
     <row r="18" s="38" customFormat="1" ht="14.25" spans="1:11">
       <c r="A18" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="24" t="s">
         <v>35</v>
       </c>
       <c r="C18" s="19">
@@ -2072,10 +2037,10 @@
         <v>17</v>
       </c>
       <c r="G18" s="20">
-        <v>22601</v>
-      </c>
-      <c r="H18" s="46" t="s">
-        <v>24</v>
+        <v>22802</v>
+      </c>
+      <c r="H18" s="21" t="s">
+        <v>21</v>
       </c>
       <c r="I18" s="20">
         <v>1</v>
@@ -2083,11 +2048,11 @@
       <c r="J18" s="22"/>
       <c r="K18" s="23"/>
     </row>
-    <row r="19" s="38" customFormat="1" ht="14.25" spans="1:11">
+    <row r="19" spans="1:11">
       <c r="A19" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="B19" s="24" t="s">
+      <c r="B19" s="18" t="s">
         <v>35</v>
       </c>
       <c r="C19" s="19">
@@ -2101,22 +2066,21 @@
         <v>17</v>
       </c>
       <c r="G19" s="20">
-        <v>22602</v>
+        <v>22804</v>
       </c>
       <c r="H19" s="21" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I19" s="20">
         <v>1</v>
       </c>
       <c r="J19" s="22"/>
-      <c r="K19" s="23"/>
-    </row>
-    <row r="20" ht="14.25" spans="1:11">
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="24" t="s">
         <v>35</v>
       </c>
       <c r="C20" s="19">
@@ -2130,72 +2094,72 @@
         <v>17</v>
       </c>
       <c r="G20" s="20">
-        <v>22604</v>
+        <v>22805</v>
       </c>
       <c r="H20" s="21" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I20" s="20">
         <v>1</v>
       </c>
       <c r="J20" s="22"/>
     </row>
-    <row r="21" ht="14.25" spans="1:11">
-      <c r="A21" s="25" t="s">
+    <row r="21" spans="1:11">
+      <c r="A21" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="B21" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="C21" s="19">
+      <c r="B21" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="49">
         <v>8002</v>
       </c>
       <c r="D21" s="20" t="s">
         <v>43</v>
       </c>
       <c r="E21" s="20"/>
-      <c r="F21" s="17" t="s">
+      <c r="F21" s="50" t="s">
         <v>17</v>
       </c>
       <c r="G21" s="20">
-        <v>22605</v>
+        <v>22806</v>
       </c>
       <c r="H21" s="21" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="I21" s="20">
         <v>1</v>
       </c>
-      <c r="J21" s="22"/>
+      <c r="J21" s="51"/>
+      <c r="K21" s="52"/>
     </row>
     <row r="22" ht="14.25" spans="1:11">
-      <c r="A22" s="47" t="s">
+      <c r="A22" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="C22" s="49">
+      <c r="B22" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="25">
         <v>8002</v>
       </c>
-      <c r="D22" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="E22" s="20"/>
-      <c r="F22" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="G22" s="20">
-        <v>22606</v>
-      </c>
-      <c r="H22" s="21" t="s">
+      <c r="D22" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="I22" s="20">
-        <v>1</v>
-      </c>
-      <c r="J22" s="51"/>
-      <c r="K22" s="52"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G22" s="25">
+        <v>22812</v>
+      </c>
+      <c r="H22" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="I22" s="25"/>
+      <c r="J22" s="22" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="23" ht="14.25" spans="1:11">
       <c r="A23" s="25" t="s">
@@ -2215,7 +2179,7 @@
         <v>17</v>
       </c>
       <c r="G23" s="25">
-        <v>22812</v>
+        <v>22814</v>
       </c>
       <c r="H23" s="25" t="s">
         <v>21</v>
@@ -2243,7 +2207,7 @@
         <v>17</v>
       </c>
       <c r="G24" s="25">
-        <v>22814</v>
+        <v>22816</v>
       </c>
       <c r="H24" s="25" t="s">
         <v>21</v>
@@ -2253,30 +2217,32 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" ht="14.25" spans="1:11">
+    <row r="25" spans="1:11">
       <c r="A25" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="B25" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C25" s="25">
+      <c r="B25" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" s="19">
         <v>8002</v>
       </c>
-      <c r="D25" s="25" t="s">
+      <c r="D25" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="E25" s="25"/>
-      <c r="F25" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="G25" s="25">
-        <v>22816</v>
-      </c>
-      <c r="H25" s="25" t="s">
+      <c r="E25" s="20"/>
+      <c r="F25" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G25" s="20">
+        <v>22818</v>
+      </c>
+      <c r="H25" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="I25" s="25"/>
+      <c r="I25" s="20">
+        <v>1</v>
+      </c>
       <c r="J25" s="22" t="s">
         <v>29</v>
       </c>
@@ -2299,7 +2265,7 @@
         <v>17</v>
       </c>
       <c r="G26" s="20">
-        <v>22618</v>
+        <v>22832</v>
       </c>
       <c r="H26" s="21" t="s">
         <v>21</v>
@@ -2308,42 +2274,44 @@
         <v>1</v>
       </c>
       <c r="J26" s="22" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="27" ht="14.25" spans="1:11">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="24" t="s">
         <v>35</v>
       </c>
       <c r="C27" s="19">
         <v>8002</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E27" s="20"/>
       <c r="F27" s="17" t="s">
         <v>17</v>
       </c>
       <c r="G27" s="20">
-        <v>22632</v>
+        <v>22834</v>
       </c>
       <c r="H27" s="21" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="I27" s="20">
         <v>1</v>
       </c>
-      <c r="J27" s="22"/>
-    </row>
-    <row r="28" ht="14.25" spans="1:11">
+      <c r="J27" s="22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
       <c r="A28" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="24" t="s">
+      <c r="B28" s="18" t="s">
         <v>35</v>
       </c>
       <c r="C28" s="19">
@@ -2357,21 +2325,23 @@
         <v>17</v>
       </c>
       <c r="G28" s="20">
-        <v>22634</v>
+        <v>22839</v>
       </c>
       <c r="H28" s="21" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="I28" s="20">
         <v>1</v>
       </c>
-      <c r="J28" s="22"/>
-    </row>
-    <row r="29" ht="14.25" spans="1:11">
+      <c r="J28" s="22" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
       <c r="A29" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="18" t="s">
+      <c r="B29" s="24" t="s">
         <v>35</v>
       </c>
       <c r="C29" s="19">
@@ -2385,7 +2355,7 @@
         <v>17</v>
       </c>
       <c r="G29" s="20">
-        <v>22639</v>
+        <v>22842</v>
       </c>
       <c r="H29" s="21" t="s">
         <v>18</v>
@@ -2397,11 +2367,11 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" ht="14.25" spans="1:11">
+    <row r="30" spans="1:11">
       <c r="A30" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="B30" s="24" t="s">
+      <c r="B30" s="18" t="s">
         <v>35</v>
       </c>
       <c r="C30" s="19">
@@ -2415,7 +2385,7 @@
         <v>17</v>
       </c>
       <c r="G30" s="20">
-        <v>22642</v>
+        <v>22845</v>
       </c>
       <c r="H30" s="21" t="s">
         <v>18</v>
@@ -2444,8 +2414,8 @@
       <c r="F31" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="G31" s="20">
-        <v>22645</v>
+      <c r="G31" s="53">
+        <v>22848</v>
       </c>
       <c r="H31" s="21" t="s">
         <v>18</v>
@@ -2457,248 +2427,227 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" ht="14.25" spans="1:11">
+    <row r="32" customFormat="1" ht="14.25" spans="1:11">
       <c r="A32" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="B32" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C32" s="39">
+      <c r="B32" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" s="25">
         <v>8002</v>
       </c>
-      <c r="D32" s="20" t="s">
+      <c r="D32" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="E32" s="20"/>
-      <c r="F32" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G32" s="39">
-        <v>22862</v>
-      </c>
-      <c r="H32" s="44" t="s">
+      <c r="E32" s="25"/>
+      <c r="F32" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G32" s="25">
+        <v>22856</v>
+      </c>
+      <c r="H32" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="I32" s="20">
-        <v>1</v>
-      </c>
-      <c r="J32" s="27" t="s">
-        <v>57</v>
-      </c>
-      <c r="K32" s="53"/>
-    </row>
-    <row r="33" ht="14.25" spans="1:11">
+      <c r="I32" s="25"/>
+      <c r="J32" s="25"/>
+    </row>
+    <row r="33" customFormat="1" ht="14.25" spans="1:10">
       <c r="A33" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="B33" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C33" s="39">
+      <c r="B33" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C33" s="25">
         <v>8002</v>
       </c>
-      <c r="D33" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="E33" s="20"/>
-      <c r="F33" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G33" s="39">
-        <v>22864</v>
-      </c>
-      <c r="H33" s="44" t="s">
+      <c r="D33" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G33" s="25">
+        <v>22858</v>
+      </c>
+      <c r="H33" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="I33" s="20">
-        <v>1</v>
-      </c>
-      <c r="J33" s="27" t="s">
-        <v>59</v>
-      </c>
-      <c r="K33" s="53"/>
-    </row>
-    <row r="34" ht="14.25" spans="1:11">
+      <c r="I33" s="25"/>
+      <c r="J33" s="25"/>
+    </row>
+    <row r="34" customFormat="1" ht="14.25" spans="1:10">
       <c r="A34" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="B34" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C34" s="39">
+      <c r="B34" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C34" s="25">
         <v>8002</v>
       </c>
-      <c r="D34" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="E34" s="20"/>
-      <c r="F34" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G34" s="39">
-        <v>22866</v>
-      </c>
-      <c r="H34" s="44" t="s">
+      <c r="D34" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G34" s="25">
+        <v>22860</v>
+      </c>
+      <c r="H34" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="I34" s="20">
-        <v>1</v>
-      </c>
-      <c r="J34" s="27" t="s">
-        <v>59</v>
-      </c>
-      <c r="K34" s="53"/>
-    </row>
-    <row r="35" ht="14.25" spans="1:11">
+      <c r="I34" s="25"/>
+      <c r="J34" s="25" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" ht="14.25" spans="1:10">
       <c r="A35" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C35" s="39">
+      <c r="B35" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C35" s="25">
         <v>8002</v>
       </c>
-      <c r="D35" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="E35" s="20"/>
-      <c r="F35" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G35" s="39">
-        <v>22868</v>
-      </c>
-      <c r="H35" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="I35" s="20">
-        <v>1</v>
-      </c>
-      <c r="J35" s="27" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="36" ht="14.25" spans="1:11">
+      <c r="D35" s="54" t="s">
+        <v>59</v>
+      </c>
+      <c r="E35" s="25"/>
+      <c r="F35" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G35" s="25">
+        <v>22874</v>
+      </c>
+      <c r="H35" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="I35" s="25"/>
+      <c r="J35" s="25" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36" ht="14.25" spans="1:10">
       <c r="A36" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="B36" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C36" s="39">
+      <c r="B36" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C36" s="25">
         <v>8002</v>
       </c>
-      <c r="D36" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E36" s="20"/>
-      <c r="F36" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G36" s="39">
-        <v>22870</v>
-      </c>
-      <c r="H36" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="I36" s="20">
-        <v>1</v>
-      </c>
-      <c r="J36" s="27" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="37" ht="14.25" spans="1:11">
+      <c r="D36" s="54" t="s">
+        <v>60</v>
+      </c>
+      <c r="E36" s="25"/>
+      <c r="F36" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G36" s="25">
+        <v>22875</v>
+      </c>
+      <c r="H36" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="I36" s="25"/>
+      <c r="J36" s="25" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" ht="27.75" spans="1:10">
       <c r="A37" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C37" s="39">
+      <c r="B37" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C37" s="25">
         <v>8002</v>
       </c>
-      <c r="D37" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="E37" s="20"/>
-      <c r="F37" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G37" s="39">
-        <v>22872</v>
-      </c>
-      <c r="H37" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="I37" s="20">
-        <v>1</v>
-      </c>
-      <c r="J37" s="27" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="38" ht="14.25" spans="1:11">
+      <c r="D37" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="E37" s="25"/>
+      <c r="F37" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G37" s="25">
+        <v>22876</v>
+      </c>
+      <c r="H37" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="I37" s="25"/>
+      <c r="J37" s="25" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38" ht="27.75" spans="1:10">
       <c r="A38" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="B38" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="C38" s="39">
+      <c r="B38" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C38" s="25">
         <v>8002</v>
       </c>
-      <c r="D38" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="E38" s="20"/>
-      <c r="F38" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G38" s="20">
-        <v>22276</v>
-      </c>
-      <c r="H38" s="21" t="s">
+      <c r="D38" s="54" t="s">
+        <v>62</v>
+      </c>
+      <c r="E38" s="25"/>
+      <c r="F38" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G38" s="25">
+        <v>22877</v>
+      </c>
+      <c r="H38" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="I38" s="20">
-        <v>1</v>
-      </c>
-      <c r="J38" s="22" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="39" ht="14.25" spans="1:11">
+      <c r="I38" s="25"/>
+      <c r="J38" s="25" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39" ht="14.25" spans="1:10">
       <c r="A39" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="B39" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C39" s="39">
+      <c r="B39" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C39" s="25">
         <v>8002</v>
       </c>
-      <c r="D39" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="E39" s="20"/>
-      <c r="F39" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G39" s="20">
-        <v>22277</v>
-      </c>
-      <c r="H39" s="21" t="s">
+      <c r="D39" s="54" t="s">
+        <v>63</v>
+      </c>
+      <c r="E39" s="25"/>
+      <c r="F39" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G39" s="25">
+        <v>22878</v>
+      </c>
+      <c r="H39" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="I39" s="20">
-        <v>1</v>
-      </c>
-      <c r="J39" s="22"/>
-    </row>
-    <row r="40" ht="14.25" spans="1:11">
+      <c r="I39" s="25"/>
+      <c r="J39" s="25" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
       <c r="A40" s="25" t="s">
         <v>34</v>
       </c>
@@ -2708,28 +2657,23 @@
       <c r="C40" s="25">
         <v>8002</v>
       </c>
-      <c r="D40" s="25" t="s">
-        <v>66</v>
+      <c r="D40" s="54" t="s">
+        <v>64</v>
       </c>
       <c r="E40" s="25"/>
       <c r="F40" s="25" t="s">
         <v>17</v>
       </c>
       <c r="G40" s="25">
-        <v>21856</v>
+        <v>22879</v>
       </c>
       <c r="H40" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I40" s="25">
-        <v>1</v>
-      </c>
-      <c r="J40" s="25" t="s">
-        <v>59</v>
-      </c>
-      <c r="K40"/>
-    </row>
-    <row r="41" customFormat="1" ht="14.25" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="I40" s="25"/>
+      <c r="J40" s="25"/>
+    </row>
+    <row r="41" ht="15" spans="1:10">
       <c r="A41" s="25" t="s">
         <v>34</v>
       </c>
@@ -2739,28 +2683,23 @@
       <c r="C41" s="25">
         <v>8002</v>
       </c>
-      <c r="D41" s="25" t="s">
-        <v>67</v>
+      <c r="D41" s="54" t="s">
+        <v>65</v>
       </c>
       <c r="E41" s="25"/>
-      <c r="F41" s="25" t="s">
+      <c r="F41" s="31" t="s">
         <v>17</v>
       </c>
       <c r="G41" s="25">
-        <v>22648</v>
+        <v>22902</v>
       </c>
       <c r="H41" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="I41" s="25">
-        <v>1</v>
-      </c>
-      <c r="J41" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="K41" s="23"/>
-    </row>
-    <row r="42" customFormat="1" ht="14.25" spans="1:11">
+      <c r="I41" s="25"/>
+      <c r="J41" s="25"/>
+    </row>
+    <row r="42" ht="14.25" spans="1:10">
       <c r="A42" s="25" t="s">
         <v>34</v>
       </c>
@@ -2770,8 +2709,8 @@
       <c r="C42" s="25">
         <v>8002</v>
       </c>
-      <c r="D42" s="25" t="s">
-        <v>68</v>
+      <c r="D42" s="54" t="s">
+        <v>66</v>
       </c>
       <c r="E42" s="25"/>
       <c r="F42" s="25" t="s">
@@ -2784,9 +2723,11 @@
         <v>21</v>
       </c>
       <c r="I42" s="25"/>
-      <c r="J42" s="25"/>
-    </row>
-    <row r="43" customFormat="1" ht="14.25" spans="1:11">
+      <c r="J42" s="25" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="43" ht="14.25" spans="1:10">
       <c r="A43" s="25" t="s">
         <v>34</v>
       </c>
@@ -2796,8 +2737,8 @@
       <c r="C43" s="25">
         <v>8002</v>
       </c>
-      <c r="D43" s="25" t="s">
-        <v>69</v>
+      <c r="D43" s="54" t="s">
+        <v>67</v>
       </c>
       <c r="E43" s="25"/>
       <c r="F43" s="25" t="s">
@@ -2810,9 +2751,11 @@
         <v>21</v>
       </c>
       <c r="I43" s="25"/>
-      <c r="J43" s="25"/>
-    </row>
-    <row r="44" customFormat="1" ht="14.25" spans="1:11">
+      <c r="J43" s="25" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="44" ht="14.25" spans="1:10">
       <c r="A44" s="25" t="s">
         <v>34</v>
       </c>
@@ -2822,15 +2765,15 @@
       <c r="C44" s="25">
         <v>8002</v>
       </c>
-      <c r="D44" s="25" t="s">
-        <v>70</v>
+      <c r="D44" s="54" t="s">
+        <v>68</v>
       </c>
       <c r="E44" s="25"/>
       <c r="F44" s="25" t="s">
         <v>17</v>
       </c>
       <c r="G44" s="25">
-        <v>22860</v>
+        <v>22818</v>
       </c>
       <c r="H44" s="25" t="s">
         <v>21</v>
@@ -2838,7 +2781,7 @@
       <c r="I44" s="25"/>
       <c r="J44" s="25"/>
     </row>
-    <row r="45" ht="14.25" spans="1:11">
+    <row r="45" ht="14.25" spans="1:10">
       <c r="A45" s="25" t="s">
         <v>34</v>
       </c>
@@ -2848,310 +2791,31 @@
       <c r="C45" s="25">
         <v>8002</v>
       </c>
-      <c r="D45" s="25" t="s">
-        <v>71</v>
+      <c r="D45" s="54" t="s">
+        <v>69</v>
       </c>
       <c r="E45" s="25"/>
       <c r="F45" s="25" t="s">
         <v>17</v>
       </c>
       <c r="G45" s="25">
-        <v>22874</v>
+        <v>22854</v>
       </c>
       <c r="H45" s="25" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I45" s="25"/>
-      <c r="J45" s="25"/>
-    </row>
-    <row r="46" ht="14.25" spans="1:11">
-      <c r="A46" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B46" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C46" s="25">
-        <v>8002</v>
-      </c>
-      <c r="D46" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="E46" s="25"/>
-      <c r="F46" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="G46" s="25">
-        <v>22875</v>
-      </c>
-      <c r="H46" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="I46" s="25"/>
-      <c r="J46" s="25"/>
-    </row>
-    <row r="47" ht="27.75" spans="1:11">
-      <c r="A47" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B47" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C47" s="25">
-        <v>8002</v>
-      </c>
-      <c r="D47" s="25" t="s">
-        <v>73</v>
-      </c>
-      <c r="E47" s="25"/>
-      <c r="F47" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="G47" s="25">
-        <v>22876</v>
-      </c>
-      <c r="H47" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="I47" s="25"/>
-      <c r="J47" s="25"/>
-    </row>
-    <row r="48" ht="27.75" spans="1:11">
-      <c r="A48" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B48" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C48" s="25">
-        <v>8002</v>
-      </c>
-      <c r="D48" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="E48" s="25"/>
-      <c r="F48" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="G48" s="25">
-        <v>22877</v>
-      </c>
-      <c r="H48" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="I48" s="25"/>
-      <c r="J48" s="25"/>
-    </row>
-    <row r="49" ht="14.25" spans="1:10">
-      <c r="A49" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B49" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C49" s="25">
-        <v>8002</v>
-      </c>
-      <c r="D49" s="25" t="s">
-        <v>75</v>
-      </c>
-      <c r="E49" s="25"/>
-      <c r="F49" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="G49" s="25">
-        <v>22878</v>
-      </c>
-      <c r="H49" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="I49" s="25"/>
-      <c r="J49" s="25"/>
-    </row>
-    <row r="50" ht="14.25" spans="1:10">
-      <c r="A50" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B50" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C50" s="25">
-        <v>8002</v>
-      </c>
-      <c r="D50" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E50" s="25"/>
-      <c r="F50" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="G50" s="25">
-        <v>22879</v>
-      </c>
-      <c r="H50" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="I50" s="25"/>
-      <c r="J50" s="25"/>
-    </row>
-    <row r="51" ht="15" spans="1:10">
-      <c r="A51" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B51" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C51" s="25">
-        <v>8002</v>
-      </c>
-      <c r="D51" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="E51" s="25"/>
-      <c r="F51" s="54" t="s">
-        <v>17</v>
-      </c>
-      <c r="G51" s="25">
-        <v>22902</v>
-      </c>
-      <c r="H51" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="I51" s="25"/>
-      <c r="J51" s="25"/>
-    </row>
-    <row r="52" ht="14.25" spans="1:10">
-      <c r="A52" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B52" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C52" s="25">
-        <v>8002</v>
-      </c>
-      <c r="D52" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="E52" s="25"/>
-      <c r="F52" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="G52" s="25">
-        <v>22856</v>
-      </c>
-      <c r="H52" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I52" s="25"/>
-      <c r="J52" s="25"/>
-    </row>
-    <row r="53" ht="14.25" spans="1:10">
-      <c r="A53" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B53" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C53" s="25">
-        <v>8002</v>
-      </c>
-      <c r="D53" s="25" t="s">
-        <v>79</v>
-      </c>
-      <c r="E53" s="25"/>
-      <c r="F53" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="G53" s="25">
-        <v>22858</v>
-      </c>
-      <c r="H53" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I53" s="25"/>
-      <c r="J53" s="25"/>
-    </row>
-    <row r="54" ht="14.25" spans="1:10">
-      <c r="A54" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B54" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C54" s="25">
-        <v>8002</v>
-      </c>
-      <c r="D54" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="E54" s="25"/>
-      <c r="F54" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="G54" s="25">
-        <v>22860</v>
-      </c>
-      <c r="H54" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I54" s="25"/>
-      <c r="J54" s="25"/>
-    </row>
-    <row r="55" ht="14.25" spans="1:10">
-      <c r="A55" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B55" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C55" s="25">
-        <v>8002</v>
-      </c>
-      <c r="D55" s="25" t="s">
-        <v>81</v>
-      </c>
-      <c r="E55" s="25"/>
-      <c r="F55" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="G55" s="25">
-        <v>22818</v>
-      </c>
-      <c r="H55" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I55" s="25"/>
-      <c r="J55" s="25"/>
-    </row>
-    <row r="56" ht="14.25" spans="1:10">
-      <c r="A56" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B56" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C56" s="25">
-        <v>8002</v>
-      </c>
-      <c r="D56" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="E56" s="25"/>
-      <c r="F56" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="G56" s="25">
-        <v>22854</v>
-      </c>
-      <c r="H56" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I56" s="25"/>
-      <c r="J56" s="25"/>
+      <c r="J45" s="25" t="s">
+        <v>27</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:N56" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:N45" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="六分厂6-1装配B线"/>
+      </filters>
+    </filterColumn>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3174,7 +2838,7 @@
     <row r="1" ht="14.25"/>
     <row r="2" s="1" customFormat="1" ht="14.25" spans="1:12">
       <c r="A2" s="4" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>35</v>
@@ -3183,7 +2847,7 @@
         <v>9004</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="E2" s="7"/>
       <c r="F2" s="4" t="s">
@@ -3191,7 +2855,7 @@
       </c>
       <c r="G2" s="7"/>
       <c r="H2" s="8" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="I2" s="7">
         <v>1</v>
@@ -3202,7 +2866,7 @@
     </row>
     <row r="3" s="1" customFormat="1" ht="14.25" spans="1:12">
       <c r="A3" s="4" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>35</v>
@@ -3211,7 +2875,7 @@
         <v>9004</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="E3" s="7"/>
       <c r="F3" s="4" t="s">
@@ -3219,7 +2883,7 @@
       </c>
       <c r="G3" s="7"/>
       <c r="H3" s="8" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="I3" s="7">
         <v>1</v>
@@ -3230,7 +2894,7 @@
     </row>
     <row r="4" s="2" customFormat="1" ht="14.25" spans="1:12">
       <c r="A4" s="12" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>35</v>
@@ -3239,7 +2903,7 @@
         <v>9004</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="12" t="s">
@@ -3259,7 +2923,7 @@
     <row r="5" customFormat="1" ht="14.25" hidden="1"/>
     <row r="6" ht="14.25" spans="1:12">
       <c r="A6" s="17" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="B6" s="18" t="s">
         <v>35</v>
@@ -3268,7 +2932,7 @@
         <v>9004</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="E6" s="20"/>
       <c r="F6" s="17" t="s">
@@ -3276,7 +2940,7 @@
       </c>
       <c r="G6" s="20"/>
       <c r="H6" s="21" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="I6" s="20">
         <v>1</v>
@@ -3287,7 +2951,7 @@
     </row>
     <row r="7" ht="14.25" spans="1:12">
       <c r="A7" s="17" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="B7" s="24" t="s">
         <v>35</v>
@@ -3296,7 +2960,7 @@
         <v>9004</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="E7" s="20"/>
       <c r="F7" s="17" t="s">
@@ -3304,7 +2968,7 @@
       </c>
       <c r="G7" s="20"/>
       <c r="H7" s="21" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="I7" s="20">
         <v>1</v>
@@ -3315,7 +2979,7 @@
     </row>
     <row r="8" ht="14.25" spans="1:12">
       <c r="A8" s="17" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="B8" s="24" t="s">
         <v>35</v>
@@ -3324,7 +2988,7 @@
         <v>9004</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="E8" s="20"/>
       <c r="F8" s="17" t="s">
@@ -3343,7 +3007,7 @@
     </row>
     <row r="9" ht="14.25" spans="1:12">
       <c r="A9" s="17" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="B9" s="18" t="s">
         <v>35</v>
@@ -3352,7 +3016,7 @@
         <v>9004</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="E9" s="20"/>
       <c r="F9" s="17" t="s">
@@ -3373,7 +3037,7 @@
     </row>
     <row r="10" ht="14.25" spans="1:12">
       <c r="A10" s="17" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="B10" s="24" t="s">
         <v>35</v>
@@ -3382,7 +3046,7 @@
         <v>9004</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="E10" s="20"/>
       <c r="F10" s="17" t="s">
@@ -3396,14 +3060,14 @@
         <v>1</v>
       </c>
       <c r="J10" s="22" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="K10" s="23"/>
       <c r="L10" s="19"/>
     </row>
     <row r="11" ht="14.25" spans="1:12">
       <c r="A11" s="17" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="B11" s="18" t="s">
         <v>35</v>
@@ -3412,7 +3076,7 @@
         <v>9004</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="E11" s="20"/>
       <c r="F11" s="17" t="s">
@@ -3426,14 +3090,14 @@
         <v>1</v>
       </c>
       <c r="J11" s="22" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="K11" s="23"/>
       <c r="L11" s="19"/>
     </row>
     <row r="12" ht="14.25" spans="1:12">
       <c r="A12" s="17" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="B12" s="24" t="s">
         <v>35</v>
@@ -3442,7 +3106,7 @@
         <v>9004</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="E12" s="20"/>
       <c r="F12" s="17" t="s">
@@ -3456,14 +3120,14 @@
         <v>1</v>
       </c>
       <c r="J12" s="22" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="K12" s="23"/>
       <c r="L12" s="19"/>
     </row>
     <row r="13" ht="14.25" spans="1:12">
       <c r="A13" s="25" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="B13" s="18" t="s">
         <v>35</v>
@@ -3472,11 +3136,11 @@
         <v>9004</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="E13" s="20"/>
       <c r="F13" s="18" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G13" s="24"/>
       <c r="H13" s="26" t="s">
@@ -3491,7 +3155,7 @@
     </row>
     <row r="14" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A14" s="12" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>12</v>
@@ -3500,7 +3164,7 @@
         <v>8001</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
@@ -3512,7 +3176,7 @@
     </row>
     <row r="15" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A15" s="12" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>12</v>
@@ -3521,7 +3185,7 @@
         <v>8001</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
@@ -3533,7 +3197,7 @@
     </row>
     <row r="16" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A16" s="12" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>12</v>
@@ -3542,7 +3206,7 @@
         <v>8001</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
@@ -3554,7 +3218,7 @@
     </row>
     <row r="17" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A17" s="12" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>12</v>
@@ -3563,7 +3227,7 @@
         <v>8001</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
@@ -3575,7 +3239,7 @@
     </row>
     <row r="18" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A18" s="12" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>12</v>
@@ -3584,7 +3248,7 @@
         <v>8001</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
@@ -3596,7 +3260,7 @@
     </row>
     <row r="19" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A19" s="12" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>12</v>
@@ -3605,7 +3269,7 @@
         <v>8001</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
@@ -3617,7 +3281,7 @@
     </row>
     <row r="20" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A20" s="12" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>12</v>
@@ -3626,7 +3290,7 @@
         <v>8001</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
@@ -3638,7 +3302,7 @@
     </row>
     <row r="21" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A21" s="12" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>12</v>
@@ -3647,7 +3311,7 @@
         <v>8001</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
@@ -3659,7 +3323,7 @@
     </row>
     <row r="22" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A22" s="12" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>12</v>
@@ -3668,7 +3332,7 @@
         <v>8001</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
@@ -3680,7 +3344,7 @@
     </row>
     <row r="23" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A23" s="12" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>12</v>
@@ -3689,7 +3353,7 @@
         <v>8001</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
@@ -3701,7 +3365,7 @@
     </row>
     <row r="24" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A24" s="12" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>12</v>
@@ -3710,7 +3374,7 @@
         <v>8001</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
@@ -3722,7 +3386,7 @@
     </row>
     <row r="25" ht="15" hidden="1" spans="1:12">
       <c r="A25" s="25" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="B25" s="18" t="s">
         <v>12</v>
@@ -3731,10 +3395,10 @@
         <v>8001</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="F25" s="18" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G25" s="24"/>
       <c r="H25" s="26" t="s">
@@ -3749,7 +3413,7 @@
     </row>
     <row r="26" s="3" customFormat="1" ht="14.25" spans="1:12">
       <c r="A26" s="32" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="B26" s="33" t="s">
         <v>35</v>
@@ -3758,7 +3422,7 @@
         <v>9004</v>
       </c>
       <c r="D26" s="35" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="E26" s="35"/>
       <c r="F26" s="32" t="s">
@@ -3772,7 +3436,7 @@
         <v>1</v>
       </c>
       <c r="J26" s="37" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/doc/六分厂6-1#装配线/点位信息.xlsx
+++ b/doc/六分厂6-1#装配线/点位信息.xlsx
@@ -1515,7 +1515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
+  <sheetPr/>
   <dimension ref="A1:K45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
@@ -1568,7 +1568,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" ht="14.25" hidden="1" spans="1:11">
+    <row r="2" ht="15" spans="1:11">
       <c r="A2" s="25" t="s">
         <v>11</v>
       </c>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="J2" s="19"/>
     </row>
-    <row r="3" ht="15" hidden="1" spans="1:11">
+    <row r="3" ht="15" spans="1:11">
       <c r="A3" s="25" t="s">
         <v>11</v>
       </c>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="J3" s="19"/>
     </row>
-    <row r="4" ht="15" hidden="1" spans="1:11">
+    <row r="4" ht="15" spans="1:11">
       <c r="A4" s="25" t="s">
         <v>11</v>
       </c>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="J4" s="19"/>
     </row>
-    <row r="5" ht="15" hidden="1" spans="1:11">
+    <row r="5" ht="15" spans="1:11">
       <c r="A5" s="25" t="s">
         <v>11</v>
       </c>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="J5" s="19"/>
     </row>
-    <row r="6" ht="15" hidden="1" spans="1:11">
+    <row r="6" ht="15" spans="1:11">
       <c r="A6" s="25" t="s">
         <v>11</v>
       </c>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="J6" s="19"/>
     </row>
-    <row r="7" s="1" customFormat="1" ht="15" hidden="1" spans="1:11">
+    <row r="7" s="1" customFormat="1" ht="15" spans="1:11">
       <c r="A7" s="25" t="s">
         <v>11</v>
       </c>
@@ -1730,7 +1730,7 @@
       <c r="J7" s="19"/>
       <c r="K7" s="23"/>
     </row>
-    <row r="8" s="1" customFormat="1" ht="15" hidden="1" spans="1:11">
+    <row r="8" s="1" customFormat="1" ht="15" spans="1:11">
       <c r="A8" s="25" t="s">
         <v>11</v>
       </c>
@@ -1757,7 +1757,7 @@
       <c r="J8" s="19"/>
       <c r="K8" s="23"/>
     </row>
-    <row r="9" s="1" customFormat="1" ht="15" hidden="1" spans="1:11">
+    <row r="9" s="1" customFormat="1" ht="15" spans="1:11">
       <c r="A9" s="25" t="s">
         <v>11</v>
       </c>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="K9" s="23"/>
     </row>
-    <row r="10" ht="15" hidden="1" spans="1:11">
+    <row r="10" ht="15" spans="1:11">
       <c r="A10" s="25" t="s">
         <v>11</v>
       </c>
@@ -1818,7 +1818,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" ht="15" hidden="1" spans="1:11">
+    <row r="11" ht="15" spans="1:11">
       <c r="A11" s="25" t="s">
         <v>11</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" ht="15" hidden="1" spans="1:11">
+    <row r="12" ht="15" spans="1:11">
       <c r="A12" s="25" t="s">
         <v>11</v>
       </c>
@@ -1865,7 +1865,7 @@
         <v>17</v>
       </c>
       <c r="G12" s="43">
-        <v>24074</v>
+        <v>24070</v>
       </c>
       <c r="H12" s="44" t="s">
         <v>32</v>
@@ -1876,7 +1876,7 @@
       <c r="J12" s="24"/>
       <c r="K12" s="38"/>
     </row>
-    <row r="13" ht="15" hidden="1" spans="1:11">
+    <row r="13" ht="15" spans="1:11">
       <c r="A13" s="25" t="s">
         <v>11</v>
       </c>
@@ -1894,7 +1894,7 @@
         <v>17</v>
       </c>
       <c r="G13" s="43">
-        <v>24094</v>
+        <v>24090</v>
       </c>
       <c r="H13" s="44" t="s">
         <v>32</v>
@@ -1933,7 +1933,7 @@
       </c>
       <c r="J14" s="22"/>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" ht="14.25" spans="1:11">
       <c r="A15" s="25" t="s">
         <v>34</v>
       </c>
@@ -2048,7 +2048,7 @@
       <c r="J18" s="22"/>
       <c r="K18" s="23"/>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" ht="14.25" spans="1:11">
       <c r="A19" s="25" t="s">
         <v>34</v>
       </c>
@@ -2076,7 +2076,7 @@
       </c>
       <c r="J19" s="22"/>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" ht="14.25" spans="1:11">
       <c r="A20" s="25" t="s">
         <v>34</v>
       </c>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="J20" s="22"/>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" ht="14.25" spans="1:11">
       <c r="A21" s="47" t="s">
         <v>34</v>
       </c>
@@ -2217,7 +2217,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" ht="14.25" spans="1:11">
       <c r="A25" s="25" t="s">
         <v>34</v>
       </c>
@@ -2277,7 +2277,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" ht="14.25" spans="1:11">
       <c r="A27" s="25" t="s">
         <v>34</v>
       </c>
@@ -2307,7 +2307,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" ht="14.25" spans="1:11">
       <c r="A28" s="25" t="s">
         <v>34</v>
       </c>
@@ -2337,7 +2337,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" ht="14.25" spans="1:11">
       <c r="A29" s="25" t="s">
         <v>34</v>
       </c>
@@ -2367,7 +2367,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" ht="14.25" spans="1:11">
       <c r="A30" s="25" t="s">
         <v>34</v>
       </c>
@@ -2647,7 +2647,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" ht="14.25" spans="1:10">
       <c r="A40" s="25" t="s">
         <v>34</v>
       </c>
@@ -2811,11 +2811,6 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:N45" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="六分厂6-1装配B线"/>
-      </filters>
-    </filterColumn>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/doc/六分厂6-1#装配线/点位信息.xlsx
+++ b/doc/六分厂6-1#装配线/点位信息.xlsx
@@ -1905,7 +1905,7 @@
       <c r="J13" s="24"/>
       <c r="K13" s="38"/>
     </row>
-    <row r="14" ht="14.25" spans="1:11">
+    <row r="14" spans="1:11">
       <c r="A14" s="25" t="s">
         <v>34</v>
       </c>

--- a/doc/六分厂6-1#装配线/点位信息.xlsx
+++ b/doc/六分厂6-1#装配线/点位信息.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Sheet3" sheetId="7" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$3:$D$26</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="99">
   <si>
     <t>设备名称</t>
   </si>
@@ -243,6 +243,12 @@
   </si>
   <si>
     <t>1150 GONO CHECK</t>
+  </si>
+  <si>
+    <t>A托盘绑定</t>
+  </si>
+  <si>
+    <t>B托盘绑定</t>
   </si>
   <si>
     <t>B线</t>
@@ -1030,7 +1036,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1157,15 +1163,15 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1185,10 +1191,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1516,7 +1519,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1564,7 +1567,7 @@
       <c r="J1" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="42" t="s">
+      <c r="K1" s="40" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1581,6 +1584,7 @@
       <c r="D2" s="18" t="s">
         <v>13</v>
       </c>
+      <c r="E2" s="19"/>
       <c r="F2" s="19" t="s">
         <v>14</v>
       </c>
@@ -1594,6 +1598,7 @@
         <v>1</v>
       </c>
       <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
     </row>
     <row r="3" ht="15" spans="1:11">
       <c r="A3" s="25" t="s">
@@ -1608,6 +1613,7 @@
       <c r="D3" s="20" t="s">
         <v>16</v>
       </c>
+      <c r="E3" s="19"/>
       <c r="F3" s="31" t="s">
         <v>17</v>
       </c>
@@ -1621,6 +1627,7 @@
         <v>1</v>
       </c>
       <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
     </row>
     <row r="4" ht="15" spans="1:11">
       <c r="A4" s="25" t="s">
@@ -1635,6 +1642,7 @@
       <c r="D4" s="20" t="s">
         <v>19</v>
       </c>
+      <c r="E4" s="19"/>
       <c r="F4" s="31" t="s">
         <v>17</v>
       </c>
@@ -1648,6 +1656,7 @@
         <v>1</v>
       </c>
       <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
     </row>
     <row r="5" ht="15" spans="1:11">
       <c r="A5" s="25" t="s">
@@ -1662,6 +1671,7 @@
       <c r="D5" s="20" t="s">
         <v>20</v>
       </c>
+      <c r="E5" s="19"/>
       <c r="F5" s="19" t="s">
         <v>17</v>
       </c>
@@ -1675,6 +1685,7 @@
         <v>1</v>
       </c>
       <c r="J5" s="19"/>
+      <c r="K5" s="19"/>
     </row>
     <row r="6" ht="15" spans="1:11">
       <c r="A6" s="25" t="s">
@@ -1689,6 +1700,7 @@
       <c r="D6" s="20" t="s">
         <v>22</v>
       </c>
+      <c r="E6" s="19"/>
       <c r="F6" s="31" t="s">
         <v>17</v>
       </c>
@@ -1702,6 +1714,7 @@
         <v>1</v>
       </c>
       <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
     </row>
     <row r="7" s="1" customFormat="1" ht="15" spans="1:11">
       <c r="A7" s="25" t="s">
@@ -1726,9 +1739,11 @@
       <c r="H7" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="19"/>
+      <c r="I7" s="19">
+        <v>1</v>
+      </c>
       <c r="J7" s="19"/>
-      <c r="K7" s="23"/>
+      <c r="K7" s="19"/>
     </row>
     <row r="8" s="1" customFormat="1" ht="15" spans="1:11">
       <c r="A8" s="25" t="s">
@@ -1753,9 +1768,11 @@
       <c r="H8" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="I8" s="19"/>
+      <c r="I8" s="19">
+        <v>1</v>
+      </c>
       <c r="J8" s="19"/>
-      <c r="K8" s="23"/>
+      <c r="K8" s="19"/>
     </row>
     <row r="9" s="1" customFormat="1" ht="15" spans="1:11">
       <c r="A9" s="25" t="s">
@@ -1780,13 +1797,13 @@
       <c r="H9" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="I9" s="20">
+      <c r="I9" s="19">
         <v>1</v>
       </c>
       <c r="J9" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="K9" s="23"/>
+      <c r="K9" s="19"/>
     </row>
     <row r="10" ht="15" spans="1:11">
       <c r="A10" s="25" t="s">
@@ -1817,6 +1834,7 @@
       <c r="J10" s="24" t="s">
         <v>29</v>
       </c>
+      <c r="K10" s="19"/>
     </row>
     <row r="11" ht="15" spans="1:11">
       <c r="A11" s="25" t="s">
@@ -1831,6 +1849,7 @@
       <c r="D11" s="20" t="s">
         <v>30</v>
       </c>
+      <c r="E11" s="19"/>
       <c r="F11" s="17" t="s">
         <v>17</v>
       </c>
@@ -1846,6 +1865,7 @@
       <c r="J11" s="24" t="s">
         <v>27</v>
       </c>
+      <c r="K11" s="19"/>
     </row>
     <row r="12" ht="15" spans="1:11">
       <c r="A12" s="25" t="s">
@@ -1864,17 +1884,17 @@
       <c r="F12" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="G12" s="43">
+      <c r="G12" s="42">
         <v>24070</v>
       </c>
-      <c r="H12" s="44" t="s">
+      <c r="H12" s="43" t="s">
         <v>32</v>
       </c>
       <c r="I12" s="20">
         <v>18</v>
       </c>
       <c r="J12" s="24"/>
-      <c r="K12" s="38"/>
+      <c r="K12" s="44"/>
     </row>
     <row r="13" ht="15" spans="1:11">
       <c r="A13" s="25" t="s">
@@ -1893,19 +1913,19 @@
       <c r="F13" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="G13" s="43">
+      <c r="G13" s="42">
         <v>24090</v>
       </c>
-      <c r="H13" s="44" t="s">
+      <c r="H13" s="43" t="s">
         <v>32</v>
       </c>
       <c r="I13" s="20">
         <v>18</v>
       </c>
       <c r="J13" s="24"/>
-      <c r="K13" s="38"/>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="K13" s="44"/>
+    </row>
+    <row r="14" ht="14.25" spans="1:11">
       <c r="A14" s="25" t="s">
         <v>34</v>
       </c>
@@ -1931,7 +1951,8 @@
       <c r="I14" s="20">
         <v>1</v>
       </c>
-      <c r="J14" s="22"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="19"/>
     </row>
     <row r="15" ht="14.25" spans="1:11">
       <c r="A15" s="25" t="s">
@@ -1959,8 +1980,8 @@
       <c r="I15" s="20">
         <v>32</v>
       </c>
-      <c r="J15" s="27"/>
-      <c r="K15" s="28"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="39"/>
     </row>
     <row r="16" ht="14.25" spans="1:11">
       <c r="A16" s="25" t="s">
@@ -1988,7 +2009,8 @@
       <c r="I16" s="20">
         <v>1</v>
       </c>
-      <c r="J16" s="42"/>
+      <c r="J16" s="40"/>
+      <c r="K16" s="19"/>
     </row>
     <row r="17" s="38" customFormat="1" ht="14.25" spans="1:11">
       <c r="A17" s="25" t="s">
@@ -2016,8 +2038,8 @@
       <c r="I17" s="20">
         <v>1</v>
       </c>
-      <c r="J17" s="22"/>
-      <c r="K17" s="23"/>
+      <c r="J17" s="24"/>
+      <c r="K17" s="19"/>
     </row>
     <row r="18" s="38" customFormat="1" ht="14.25" spans="1:11">
       <c r="A18" s="25" t="s">
@@ -2045,8 +2067,8 @@
       <c r="I18" s="20">
         <v>1</v>
       </c>
-      <c r="J18" s="22"/>
-      <c r="K18" s="23"/>
+      <c r="J18" s="24"/>
+      <c r="K18" s="19"/>
     </row>
     <row r="19" ht="14.25" spans="1:11">
       <c r="A19" s="25" t="s">
@@ -2074,7 +2096,8 @@
       <c r="I19" s="20">
         <v>1</v>
       </c>
-      <c r="J19" s="22"/>
+      <c r="J19" s="24"/>
+      <c r="K19" s="19"/>
     </row>
     <row r="20" ht="14.25" spans="1:11">
       <c r="A20" s="25" t="s">
@@ -2102,7 +2125,8 @@
       <c r="I20" s="20">
         <v>1</v>
       </c>
-      <c r="J20" s="22"/>
+      <c r="J20" s="24"/>
+      <c r="K20" s="19"/>
     </row>
     <row r="21" ht="14.25" spans="1:11">
       <c r="A21" s="47" t="s">
@@ -2131,7 +2155,7 @@
         <v>1</v>
       </c>
       <c r="J21" s="51"/>
-      <c r="K21" s="52"/>
+      <c r="K21" s="49"/>
     </row>
     <row r="22" ht="14.25" spans="1:11">
       <c r="A22" s="25" t="s">
@@ -2156,10 +2180,13 @@
       <c r="H22" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="I22" s="25"/>
-      <c r="J22" s="22" t="s">
+      <c r="I22" s="20">
+        <v>1</v>
+      </c>
+      <c r="J22" s="24" t="s">
         <v>29</v>
       </c>
+      <c r="K22" s="19"/>
     </row>
     <row r="23" ht="14.25" spans="1:11">
       <c r="A23" s="25" t="s">
@@ -2184,10 +2211,13 @@
       <c r="H23" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="I23" s="25"/>
-      <c r="J23" s="22" t="s">
+      <c r="I23" s="20">
+        <v>1</v>
+      </c>
+      <c r="J23" s="24" t="s">
         <v>29</v>
       </c>
+      <c r="K23" s="19"/>
     </row>
     <row r="24" ht="14.25" spans="1:11">
       <c r="A24" s="25" t="s">
@@ -2212,10 +2242,13 @@
       <c r="H24" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="I24" s="25"/>
-      <c r="J24" s="22" t="s">
+      <c r="I24" s="20">
+        <v>1</v>
+      </c>
+      <c r="J24" s="24" t="s">
         <v>27</v>
       </c>
+      <c r="K24" s="19"/>
     </row>
     <row r="25" ht="14.25" spans="1:11">
       <c r="A25" s="25" t="s">
@@ -2243,9 +2276,10 @@
       <c r="I25" s="20">
         <v>1</v>
       </c>
-      <c r="J25" s="22" t="s">
+      <c r="J25" s="24" t="s">
         <v>29</v>
       </c>
+      <c r="K25" s="19"/>
     </row>
     <row r="26" ht="14.25" spans="1:11">
       <c r="A26" s="25" t="s">
@@ -2273,9 +2307,10 @@
       <c r="I26" s="20">
         <v>1</v>
       </c>
-      <c r="J26" s="22" t="s">
+      <c r="J26" s="24" t="s">
         <v>50</v>
       </c>
+      <c r="K26" s="19"/>
     </row>
     <row r="27" ht="14.25" spans="1:11">
       <c r="A27" s="25" t="s">
@@ -2303,9 +2338,10 @@
       <c r="I27" s="20">
         <v>1</v>
       </c>
-      <c r="J27" s="22" t="s">
+      <c r="J27" s="24" t="s">
         <v>50</v>
       </c>
+      <c r="K27" s="19"/>
     </row>
     <row r="28" ht="14.25" spans="1:11">
       <c r="A28" s="25" t="s">
@@ -2333,9 +2369,10 @@
       <c r="I28" s="20">
         <v>1</v>
       </c>
-      <c r="J28" s="22" t="s">
+      <c r="J28" s="24" t="s">
         <v>29</v>
       </c>
+      <c r="K28" s="19"/>
     </row>
     <row r="29" ht="14.25" spans="1:11">
       <c r="A29" s="25" t="s">
@@ -2363,9 +2400,10 @@
       <c r="I29" s="20">
         <v>1</v>
       </c>
-      <c r="J29" s="22" t="s">
+      <c r="J29" s="24" t="s">
         <v>29</v>
       </c>
+      <c r="K29" s="19"/>
     </row>
     <row r="30" ht="14.25" spans="1:11">
       <c r="A30" s="25" t="s">
@@ -2393,9 +2431,10 @@
       <c r="I30" s="20">
         <v>1</v>
       </c>
-      <c r="J30" s="22" t="s">
+      <c r="J30" s="24" t="s">
         <v>29</v>
       </c>
+      <c r="K30" s="19"/>
     </row>
     <row r="31" ht="14.25" spans="1:11">
       <c r="A31" s="25" t="s">
@@ -2414,7 +2453,7 @@
       <c r="F31" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="G31" s="53">
+      <c r="G31" s="52">
         <v>22848</v>
       </c>
       <c r="H31" s="21" t="s">
@@ -2423,9 +2462,10 @@
       <c r="I31" s="20">
         <v>1</v>
       </c>
-      <c r="J31" s="22" t="s">
+      <c r="J31" s="24" t="s">
         <v>29</v>
       </c>
+      <c r="K31" s="19"/>
     </row>
     <row r="32" customFormat="1" ht="14.25" spans="1:11">
       <c r="A32" s="25" t="s">
@@ -2450,10 +2490,13 @@
       <c r="H32" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="I32" s="25"/>
+      <c r="I32" s="20">
+        <v>1</v>
+      </c>
       <c r="J32" s="25"/>
-    </row>
-    <row r="33" customFormat="1" ht="14.25" spans="1:10">
+      <c r="K32" s="19"/>
+    </row>
+    <row r="33" customFormat="1" ht="14.25" spans="1:11">
       <c r="A33" s="25" t="s">
         <v>34</v>
       </c>
@@ -2476,10 +2519,13 @@
       <c r="H33" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="I33" s="25"/>
+      <c r="I33" s="20">
+        <v>1</v>
+      </c>
       <c r="J33" s="25"/>
-    </row>
-    <row r="34" customFormat="1" ht="14.25" spans="1:10">
+      <c r="K33" s="19"/>
+    </row>
+    <row r="34" customFormat="1" ht="14.25" spans="1:11">
       <c r="A34" s="25" t="s">
         <v>34</v>
       </c>
@@ -2502,12 +2548,15 @@
       <c r="H34" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="I34" s="25"/>
+      <c r="I34" s="20">
+        <v>1</v>
+      </c>
       <c r="J34" s="25" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="35" ht="14.25" spans="1:10">
+      <c r="K34" s="19"/>
+    </row>
+    <row r="35" ht="14.25" spans="1:11">
       <c r="A35" s="25" t="s">
         <v>34</v>
       </c>
@@ -2517,7 +2566,7 @@
       <c r="C35" s="25">
         <v>8002</v>
       </c>
-      <c r="D35" s="54" t="s">
+      <c r="D35" s="53" t="s">
         <v>59</v>
       </c>
       <c r="E35" s="25"/>
@@ -2530,12 +2579,15 @@
       <c r="H35" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="I35" s="25"/>
+      <c r="I35" s="20">
+        <v>1</v>
+      </c>
       <c r="J35" s="25" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="36" ht="14.25" spans="1:10">
+      <c r="K35" s="19"/>
+    </row>
+    <row r="36" ht="14.25" spans="1:11">
       <c r="A36" s="25" t="s">
         <v>34</v>
       </c>
@@ -2545,7 +2597,7 @@
       <c r="C36" s="25">
         <v>8002</v>
       </c>
-      <c r="D36" s="54" t="s">
+      <c r="D36" s="53" t="s">
         <v>60</v>
       </c>
       <c r="E36" s="25"/>
@@ -2558,12 +2610,15 @@
       <c r="H36" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="I36" s="25"/>
+      <c r="I36" s="20">
+        <v>1</v>
+      </c>
       <c r="J36" s="25" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="37" ht="27.75" spans="1:10">
+      <c r="K36" s="19"/>
+    </row>
+    <row r="37" ht="27.75" spans="1:11">
       <c r="A37" s="25" t="s">
         <v>34</v>
       </c>
@@ -2573,7 +2628,7 @@
       <c r="C37" s="25">
         <v>8002</v>
       </c>
-      <c r="D37" s="54" t="s">
+      <c r="D37" s="53" t="s">
         <v>61</v>
       </c>
       <c r="E37" s="25"/>
@@ -2586,12 +2641,15 @@
       <c r="H37" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="I37" s="25"/>
+      <c r="I37" s="20">
+        <v>1</v>
+      </c>
       <c r="J37" s="25" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="38" ht="27.75" spans="1:10">
+      <c r="K37" s="19"/>
+    </row>
+    <row r="38" ht="27.75" spans="1:11">
       <c r="A38" s="25" t="s">
         <v>34</v>
       </c>
@@ -2601,7 +2659,7 @@
       <c r="C38" s="25">
         <v>8002</v>
       </c>
-      <c r="D38" s="54" t="s">
+      <c r="D38" s="53" t="s">
         <v>62</v>
       </c>
       <c r="E38" s="25"/>
@@ -2614,12 +2672,15 @@
       <c r="H38" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="I38" s="25"/>
+      <c r="I38" s="20">
+        <v>1</v>
+      </c>
       <c r="J38" s="25" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="39" ht="14.25" spans="1:10">
+      <c r="K38" s="19"/>
+    </row>
+    <row r="39" ht="14.25" spans="1:11">
       <c r="A39" s="25" t="s">
         <v>34</v>
       </c>
@@ -2629,7 +2690,7 @@
       <c r="C39" s="25">
         <v>8002</v>
       </c>
-      <c r="D39" s="54" t="s">
+      <c r="D39" s="53" t="s">
         <v>63</v>
       </c>
       <c r="E39" s="25"/>
@@ -2642,12 +2703,15 @@
       <c r="H39" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="I39" s="25"/>
+      <c r="I39" s="20">
+        <v>1</v>
+      </c>
       <c r="J39" s="25" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="40" ht="14.25" spans="1:10">
+      <c r="K39" s="19"/>
+    </row>
+    <row r="40" ht="14.25" spans="1:11">
       <c r="A40" s="25" t="s">
         <v>34</v>
       </c>
@@ -2657,7 +2721,7 @@
       <c r="C40" s="25">
         <v>8002</v>
       </c>
-      <c r="D40" s="54" t="s">
+      <c r="D40" s="53" t="s">
         <v>64</v>
       </c>
       <c r="E40" s="25"/>
@@ -2670,10 +2734,13 @@
       <c r="H40" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="I40" s="25"/>
+      <c r="I40" s="20">
+        <v>1</v>
+      </c>
       <c r="J40" s="25"/>
-    </row>
-    <row r="41" ht="15" spans="1:10">
+      <c r="K40" s="19"/>
+    </row>
+    <row r="41" ht="15" spans="1:11">
       <c r="A41" s="25" t="s">
         <v>34</v>
       </c>
@@ -2683,7 +2750,7 @@
       <c r="C41" s="25">
         <v>8002</v>
       </c>
-      <c r="D41" s="54" t="s">
+      <c r="D41" s="53" t="s">
         <v>65</v>
       </c>
       <c r="E41" s="25"/>
@@ -2696,10 +2763,13 @@
       <c r="H41" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="I41" s="25"/>
+      <c r="I41" s="20">
+        <v>1</v>
+      </c>
       <c r="J41" s="25"/>
-    </row>
-    <row r="42" ht="14.25" spans="1:10">
+      <c r="K41" s="19"/>
+    </row>
+    <row r="42" ht="14.25" spans="1:11">
       <c r="A42" s="25" t="s">
         <v>34</v>
       </c>
@@ -2709,7 +2779,7 @@
       <c r="C42" s="25">
         <v>8002</v>
       </c>
-      <c r="D42" s="54" t="s">
+      <c r="D42" s="53" t="s">
         <v>66</v>
       </c>
       <c r="E42" s="25"/>
@@ -2722,12 +2792,15 @@
       <c r="H42" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="I42" s="25"/>
+      <c r="I42" s="20">
+        <v>1</v>
+      </c>
       <c r="J42" s="25" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="43" ht="14.25" spans="1:10">
+      <c r="K42" s="19"/>
+    </row>
+    <row r="43" ht="14.25" spans="1:11">
       <c r="A43" s="25" t="s">
         <v>34</v>
       </c>
@@ -2737,7 +2810,7 @@
       <c r="C43" s="25">
         <v>8002</v>
       </c>
-      <c r="D43" s="54" t="s">
+      <c r="D43" s="53" t="s">
         <v>67</v>
       </c>
       <c r="E43" s="25"/>
@@ -2750,12 +2823,15 @@
       <c r="H43" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="I43" s="25"/>
+      <c r="I43" s="20">
+        <v>1</v>
+      </c>
       <c r="J43" s="25" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="44" ht="14.25" spans="1:10">
+      <c r="K43" s="19"/>
+    </row>
+    <row r="44" ht="14.25" spans="1:11">
       <c r="A44" s="25" t="s">
         <v>34</v>
       </c>
@@ -2765,7 +2841,7 @@
       <c r="C44" s="25">
         <v>8002</v>
       </c>
-      <c r="D44" s="54" t="s">
+      <c r="D44" s="53" t="s">
         <v>68</v>
       </c>
       <c r="E44" s="25"/>
@@ -2778,10 +2854,13 @@
       <c r="H44" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="I44" s="25"/>
+      <c r="I44" s="20">
+        <v>1</v>
+      </c>
       <c r="J44" s="25"/>
-    </row>
-    <row r="45" ht="14.25" spans="1:10">
+      <c r="K44" s="19"/>
+    </row>
+    <row r="45" ht="14.25" spans="1:11">
       <c r="A45" s="25" t="s">
         <v>34</v>
       </c>
@@ -2791,7 +2870,7 @@
       <c r="C45" s="25">
         <v>8002</v>
       </c>
-      <c r="D45" s="54" t="s">
+      <c r="D45" s="53" t="s">
         <v>69</v>
       </c>
       <c r="E45" s="25"/>
@@ -2804,13 +2883,74 @@
       <c r="H45" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="I45" s="25"/>
+      <c r="I45" s="20">
+        <v>1</v>
+      </c>
       <c r="J45" s="25" t="s">
         <v>27</v>
       </c>
+      <c r="K45" s="19"/>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B46" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C46" s="25">
+        <v>8002</v>
+      </c>
+      <c r="D46" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="E46" s="19"/>
+      <c r="F46" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G46" s="39">
+        <v>20005</v>
+      </c>
+      <c r="H46" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="I46" s="20">
+        <v>1</v>
+      </c>
+      <c r="J46" s="19"/>
+      <c r="K46" s="19"/>
+    </row>
+    <row r="47" ht="14.25" spans="1:11">
+      <c r="A47" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B47" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C47" s="25">
+        <v>8002</v>
+      </c>
+      <c r="D47" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="E47" s="19"/>
+      <c r="F47" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G47" s="39">
+        <v>20000</v>
+      </c>
+      <c r="H47" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="I47" s="20">
+        <v>1</v>
+      </c>
+      <c r="J47" s="19"/>
+      <c r="K47" s="19"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:N45" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:N47" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2833,7 +2973,7 @@
     <row r="1" ht="14.25"/>
     <row r="2" s="1" customFormat="1" ht="14.25" spans="1:12">
       <c r="A2" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>35</v>
@@ -2842,7 +2982,7 @@
         <v>9004</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E2" s="7"/>
       <c r="F2" s="4" t="s">
@@ -2850,7 +2990,7 @@
       </c>
       <c r="G2" s="7"/>
       <c r="H2" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I2" s="7">
         <v>1</v>
@@ -2861,7 +3001,7 @@
     </row>
     <row r="3" s="1" customFormat="1" ht="14.25" spans="1:12">
       <c r="A3" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>35</v>
@@ -2870,7 +3010,7 @@
         <v>9004</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E3" s="7"/>
       <c r="F3" s="4" t="s">
@@ -2878,7 +3018,7 @@
       </c>
       <c r="G3" s="7"/>
       <c r="H3" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I3" s="7">
         <v>1</v>
@@ -2889,7 +3029,7 @@
     </row>
     <row r="4" s="2" customFormat="1" ht="14.25" spans="1:12">
       <c r="A4" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>35</v>
@@ -2898,7 +3038,7 @@
         <v>9004</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="12" t="s">
@@ -2918,7 +3058,7 @@
     <row r="5" customFormat="1" ht="14.25" hidden="1"/>
     <row r="6" ht="14.25" spans="1:12">
       <c r="A6" s="17" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B6" s="18" t="s">
         <v>35</v>
@@ -2927,7 +3067,7 @@
         <v>9004</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E6" s="20"/>
       <c r="F6" s="17" t="s">
@@ -2935,7 +3075,7 @@
       </c>
       <c r="G6" s="20"/>
       <c r="H6" s="21" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I6" s="20">
         <v>1</v>
@@ -2946,7 +3086,7 @@
     </row>
     <row r="7" ht="14.25" spans="1:12">
       <c r="A7" s="17" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B7" s="24" t="s">
         <v>35</v>
@@ -2955,7 +3095,7 @@
         <v>9004</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E7" s="20"/>
       <c r="F7" s="17" t="s">
@@ -2963,7 +3103,7 @@
       </c>
       <c r="G7" s="20"/>
       <c r="H7" s="21" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I7" s="20">
         <v>1</v>
@@ -2974,7 +3114,7 @@
     </row>
     <row r="8" ht="14.25" spans="1:12">
       <c r="A8" s="17" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B8" s="24" t="s">
         <v>35</v>
@@ -2983,7 +3123,7 @@
         <v>9004</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E8" s="20"/>
       <c r="F8" s="17" t="s">
@@ -3002,7 +3142,7 @@
     </row>
     <row r="9" ht="14.25" spans="1:12">
       <c r="A9" s="17" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B9" s="18" t="s">
         <v>35</v>
@@ -3011,7 +3151,7 @@
         <v>9004</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E9" s="20"/>
       <c r="F9" s="17" t="s">
@@ -3032,7 +3172,7 @@
     </row>
     <row r="10" ht="14.25" spans="1:12">
       <c r="A10" s="17" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B10" s="24" t="s">
         <v>35</v>
@@ -3041,7 +3181,7 @@
         <v>9004</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E10" s="20"/>
       <c r="F10" s="17" t="s">
@@ -3062,7 +3202,7 @@
     </row>
     <row r="11" ht="14.25" spans="1:12">
       <c r="A11" s="17" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B11" s="18" t="s">
         <v>35</v>
@@ -3071,7 +3211,7 @@
         <v>9004</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E11" s="20"/>
       <c r="F11" s="17" t="s">
@@ -3092,7 +3232,7 @@
     </row>
     <row r="12" ht="14.25" spans="1:12">
       <c r="A12" s="17" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B12" s="24" t="s">
         <v>35</v>
@@ -3101,7 +3241,7 @@
         <v>9004</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E12" s="20"/>
       <c r="F12" s="17" t="s">
@@ -3122,7 +3262,7 @@
     </row>
     <row r="13" ht="14.25" spans="1:12">
       <c r="A13" s="25" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B13" s="18" t="s">
         <v>35</v>
@@ -3131,11 +3271,11 @@
         <v>9004</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E13" s="20"/>
       <c r="F13" s="18" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G13" s="24"/>
       <c r="H13" s="26" t="s">
@@ -3150,7 +3290,7 @@
     </row>
     <row r="14" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A14" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>12</v>
@@ -3159,7 +3299,7 @@
         <v>8001</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
@@ -3171,7 +3311,7 @@
     </row>
     <row r="15" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A15" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>12</v>
@@ -3180,7 +3320,7 @@
         <v>8001</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
@@ -3192,7 +3332,7 @@
     </row>
     <row r="16" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A16" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>12</v>
@@ -3201,7 +3341,7 @@
         <v>8001</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
@@ -3213,7 +3353,7 @@
     </row>
     <row r="17" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A17" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>12</v>
@@ -3222,7 +3362,7 @@
         <v>8001</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
@@ -3234,7 +3374,7 @@
     </row>
     <row r="18" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A18" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>12</v>
@@ -3243,7 +3383,7 @@
         <v>8001</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
@@ -3255,7 +3395,7 @@
     </row>
     <row r="19" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A19" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>12</v>
@@ -3264,7 +3404,7 @@
         <v>8001</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
@@ -3276,7 +3416,7 @@
     </row>
     <row r="20" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A20" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>12</v>
@@ -3285,7 +3425,7 @@
         <v>8001</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
@@ -3297,7 +3437,7 @@
     </row>
     <row r="21" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A21" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>12</v>
@@ -3306,7 +3446,7 @@
         <v>8001</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
@@ -3318,7 +3458,7 @@
     </row>
     <row r="22" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A22" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>12</v>
@@ -3327,7 +3467,7 @@
         <v>8001</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
@@ -3339,7 +3479,7 @@
     </row>
     <row r="23" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A23" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>12</v>
@@ -3348,7 +3488,7 @@
         <v>8001</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
@@ -3360,7 +3500,7 @@
     </row>
     <row r="24" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A24" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>12</v>
@@ -3369,7 +3509,7 @@
         <v>8001</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
@@ -3381,7 +3521,7 @@
     </row>
     <row r="25" ht="15" hidden="1" spans="1:12">
       <c r="A25" s="25" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B25" s="18" t="s">
         <v>12</v>
@@ -3390,10 +3530,10 @@
         <v>8001</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F25" s="18" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G25" s="24"/>
       <c r="H25" s="26" t="s">
@@ -3408,7 +3548,7 @@
     </row>
     <row r="26" s="3" customFormat="1" ht="14.25" spans="1:12">
       <c r="A26" s="32" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B26" s="33" t="s">
         <v>35</v>
@@ -3417,7 +3557,7 @@
         <v>9004</v>
       </c>
       <c r="D26" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E26" s="35"/>
       <c r="F26" s="32" t="s">

--- a/doc/六分厂6-1#装配线/点位信息.xlsx
+++ b/doc/六分厂6-1#装配线/点位信息.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\C2300040802\Desktop\NTP\doc\六分厂6-1#装配线\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="19635" windowHeight="7695"/>
   </bookViews>
@@ -173,13 +178,13 @@
     <t>正游隙检测值</t>
   </si>
   <si>
+    <t>游隙压力值</t>
+  </si>
+  <si>
+    <t>位移量</t>
+  </si>
+  <si>
     <t>负游隙检测值</t>
-  </si>
-  <si>
-    <t>位移量</t>
-  </si>
-  <si>
-    <t>铆接前成型高度</t>
   </si>
   <si>
     <t>密封圈压装压力</t>
@@ -2157,7 +2162,7 @@
       <c r="J21" s="51"/>
       <c r="K21" s="49"/>
     </row>
-    <row r="22" ht="14.25" spans="1:11">
+    <row r="22" spans="1:11">
       <c r="A22" s="25" t="s">
         <v>34</v>
       </c>
@@ -2215,7 +2220,7 @@
         <v>1</v>
       </c>
       <c r="J23" s="24" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K23" s="19"/>
     </row>
@@ -2246,7 +2251,7 @@
         <v>1</v>
       </c>
       <c r="J24" s="24" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K24" s="19"/>
     </row>
@@ -2254,13 +2259,13 @@
       <c r="A25" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="B25" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C25" s="19">
+      <c r="B25" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" s="25">
         <v>8002</v>
       </c>
-      <c r="D25" s="20" t="s">
+      <c r="D25" s="47" t="s">
         <v>48</v>
       </c>
       <c r="E25" s="20"/>
@@ -2272,9 +2277,6 @@
       </c>
       <c r="H25" s="21" t="s">
         <v>21</v>
-      </c>
-      <c r="I25" s="20">
-        <v>1</v>
       </c>
       <c r="J25" s="24" t="s">
         <v>29</v>
@@ -2891,7 +2893,7 @@
       </c>
       <c r="K45" s="19"/>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" ht="14.25" spans="1:11">
       <c r="A46" s="25" t="s">
         <v>34</v>
       </c>

--- a/doc/六分厂6-1#装配线/点位信息.xlsx
+++ b/doc/六分厂6-1#装配线/点位信息.xlsx
@@ -17,7 +17,7 @@
     <sheet name="Sheet3" sheetId="7" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$P$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$3:$D$26</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -38,12 +38,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="101">
+  <si>
+    <t>设备编号</t>
+  </si>
   <si>
     <t>设备名称</t>
   </si>
   <si>
     <t>PLC_IP</t>
+  </si>
+  <si>
+    <t>功能分类</t>
   </si>
   <si>
     <t>PLC_Port</t>
@@ -1041,7 +1047,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1167,6 +1173,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1524,25 +1533,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="14.875" customWidth="1"/>
-    <col min="3" max="3" width="13.5" customWidth="1"/>
-    <col min="4" max="4" width="24.5" style="28" customWidth="1"/>
-    <col min="5" max="5" width="8.375" customWidth="1"/>
-    <col min="6" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="7" width="10.25" style="39" customWidth="1"/>
-    <col min="8" max="8" width="9.875" customWidth="1"/>
-    <col min="9" max="9" width="7.375" customWidth="1"/>
-    <col min="10" max="10" width="12.625" customWidth="1"/>
-    <col min="11" max="11" width="12.625" style="23" customWidth="1"/>
-    <col min="13" max="13" width="25.625" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="14.875" customWidth="1"/>
+    <col min="4" max="5" width="13.5" customWidth="1"/>
+    <col min="6" max="6" width="24.5" style="28" customWidth="1"/>
+    <col min="7" max="7" width="8.375" customWidth="1"/>
+    <col min="8" max="8" width="7.125" customWidth="1"/>
+    <col min="9" max="9" width="10.25" style="39" customWidth="1"/>
+    <col min="10" max="10" width="9.875" customWidth="1"/>
+    <col min="11" max="11" width="7.375" customWidth="1"/>
+    <col min="12" max="12" width="12.625" customWidth="1"/>
+    <col min="13" max="13" width="12.625" style="23" customWidth="1"/>
+    <col min="15" max="15" width="25.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:11">
-      <c r="A1" s="40" t="s">
+    <row r="1" ht="14.25" spans="1:13">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="40" t="s">
@@ -1551,22 +1561,22 @@
       <c r="C1" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="41" t="s">
+      <c r="D1" s="40" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="40" t="s">
+      <c r="F1" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="41" t="s">
+      <c r="G1" s="40" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="40" t="s">
+      <c r="I1" s="41" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="40" t="s">
@@ -1575,1384 +1585,1574 @@
       <c r="K1" s="40" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" ht="15" spans="1:11">
+      <c r="L1" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="40" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" ht="15" spans="1:13">
       <c r="A2" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="31">
+        <v>13</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="42"/>
+      <c r="E2" s="31">
         <v>8001</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="F2" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="39">
+        <v>594</v>
+      </c>
+      <c r="J2" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="20">
+        <v>1</v>
+      </c>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+    </row>
+    <row r="3" ht="15" spans="1:13">
+      <c r="A3" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19" t="s">
+      <c r="B3" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="39">
-        <v>594</v>
-      </c>
-      <c r="H2" s="20" t="s">
+      <c r="D3" s="42"/>
+      <c r="E3" s="31">
+        <v>8001</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="19"/>
+      <c r="H3" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="39">
+        <v>24000</v>
+      </c>
+      <c r="J3" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="19">
+        <v>1</v>
+      </c>
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
+    </row>
+    <row r="4" ht="15" spans="1:13">
+      <c r="A4" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="42"/>
+      <c r="E4" s="31">
+        <v>8001</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="19"/>
+      <c r="H4" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="39">
+        <v>24001</v>
+      </c>
+      <c r="J4" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" s="19">
+        <v>1</v>
+      </c>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+    </row>
+    <row r="5" ht="15" spans="1:13">
+      <c r="A5" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="42"/>
+      <c r="E5" s="31">
+        <v>8001</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5" s="39">
+        <v>24002</v>
+      </c>
+      <c r="J5" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5" s="19">
+        <v>1</v>
+      </c>
+      <c r="L5" s="19"/>
+      <c r="M5" s="19"/>
+    </row>
+    <row r="6" ht="15" spans="1:13">
+      <c r="A6" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="42"/>
+      <c r="E6" s="31">
+        <v>8001</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="19"/>
+      <c r="H6" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" s="39">
+        <v>24004</v>
+      </c>
+      <c r="J6" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" s="19">
+        <v>1</v>
+      </c>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="15" spans="1:13">
+      <c r="A7" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="42"/>
+      <c r="E7" s="31">
+        <v>8001</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="20"/>
+      <c r="H7" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" s="39">
+        <v>24008</v>
+      </c>
+      <c r="J7" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="K7" s="19">
+        <v>1</v>
+      </c>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="15" spans="1:13">
+      <c r="A8" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="42"/>
+      <c r="E8" s="31">
+        <v>8001</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="20"/>
+      <c r="H8" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="I8" s="39">
+        <v>24009</v>
+      </c>
+      <c r="J8" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="K8" s="19">
+        <v>1</v>
+      </c>
+      <c r="L8" s="19"/>
+      <c r="M8" s="19"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="15" spans="1:13">
+      <c r="A9" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="42"/>
+      <c r="E9" s="31">
+        <v>8001</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" s="20"/>
+      <c r="H9" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="I9" s="39">
+        <v>24039</v>
+      </c>
+      <c r="J9" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="K9" s="19">
+        <v>1</v>
+      </c>
+      <c r="L9" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="M9" s="19"/>
+    </row>
+    <row r="10" ht="15" spans="1:13">
+      <c r="A10" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="42"/>
+      <c r="E10" s="31">
+        <v>8001</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" s="20"/>
+      <c r="H10" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" s="39">
+        <v>24031</v>
+      </c>
+      <c r="J10" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="K10" s="20">
+        <v>1</v>
+      </c>
+      <c r="L10" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="M10" s="19"/>
+    </row>
+    <row r="11" ht="15" spans="1:13">
+      <c r="A11" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="42"/>
+      <c r="E11" s="31">
+        <v>8001</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" s="19"/>
+      <c r="H11" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="I11" s="39">
+        <v>24012</v>
+      </c>
+      <c r="J11" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="K11" s="20">
+        <v>1</v>
+      </c>
+      <c r="L11" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="M11" s="19"/>
+    </row>
+    <row r="12" ht="15" spans="1:13">
+      <c r="A12" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="42"/>
+      <c r="E12" s="31">
+        <v>8001</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="20"/>
+      <c r="H12" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="I12" s="43">
+        <v>24070</v>
+      </c>
+      <c r="J12" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="K12" s="20">
+        <v>18</v>
+      </c>
+      <c r="L12" s="24"/>
+      <c r="M12" s="45"/>
+    </row>
+    <row r="13" ht="15" spans="1:13">
+      <c r="A13" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="42"/>
+      <c r="E13" s="31">
+        <v>8001</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" s="20"/>
+      <c r="H13" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="I13" s="43">
+        <v>24090</v>
+      </c>
+      <c r="J13" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="K13" s="20">
+        <v>18</v>
+      </c>
+      <c r="L13" s="24"/>
+      <c r="M13" s="45"/>
+    </row>
+    <row r="14" ht="14.25" spans="1:13">
+      <c r="A14" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19">
+        <v>8002</v>
+      </c>
+      <c r="F14" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="20">
-        <v>1</v>
-      </c>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-    </row>
-    <row r="3" ht="15" spans="1:11">
-      <c r="A3" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="31">
-        <v>8001</v>
-      </c>
-      <c r="D3" s="20" t="s">
+      <c r="G14" s="20"/>
+      <c r="H14" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="19"/>
-      <c r="F3" s="31" t="s">
+      <c r="I14" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="J14" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="39">
-        <v>24000</v>
-      </c>
-      <c r="H3" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="19">
-        <v>1</v>
-      </c>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19"/>
-    </row>
-    <row r="4" ht="15" spans="1:11">
-      <c r="A4" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="31">
-        <v>8001</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="19"/>
-      <c r="F4" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="39">
-        <v>24001</v>
-      </c>
-      <c r="H4" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="I4" s="19">
-        <v>1</v>
-      </c>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-    </row>
-    <row r="5" ht="15" spans="1:11">
-      <c r="A5" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="31">
-        <v>8001</v>
-      </c>
-      <c r="D5" s="20" t="s">
+      <c r="K14" s="20">
+        <v>1</v>
+      </c>
+      <c r="L14" s="24"/>
+      <c r="M14" s="19"/>
+    </row>
+    <row r="15" ht="14.25" spans="1:13">
+      <c r="A15" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19">
+        <v>8002</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="G15" s="20"/>
+      <c r="H15" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="I15" s="20">
+        <v>22882</v>
+      </c>
+      <c r="J15" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="K15" s="20">
+        <v>32</v>
+      </c>
+      <c r="L15" s="18"/>
+      <c r="M15" s="39"/>
+    </row>
+    <row r="16" ht="14.25" spans="1:13">
+      <c r="A16" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19">
+        <v>8002</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="G16" s="20"/>
+      <c r="H16" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="I16" s="20">
+        <v>22800</v>
+      </c>
+      <c r="J16" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="K16" s="20">
+        <v>1</v>
+      </c>
+      <c r="L16" s="40"/>
+      <c r="M16" s="19"/>
+    </row>
+    <row r="17" s="38" customFormat="1" ht="14.25" spans="1:13">
+      <c r="A17" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19">
+        <v>8002</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="G17" s="20"/>
+      <c r="H17" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="I17" s="20">
+        <v>22801</v>
+      </c>
+      <c r="J17" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="K17" s="20">
+        <v>1</v>
+      </c>
+      <c r="L17" s="24"/>
+      <c r="M17" s="19"/>
+    </row>
+    <row r="18" s="38" customFormat="1" ht="14.25" spans="1:13">
+      <c r="A18" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19">
+        <v>8002</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G18" s="20"/>
+      <c r="H18" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="I18" s="20">
+        <v>22802</v>
+      </c>
+      <c r="J18" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="K18" s="20">
+        <v>1</v>
+      </c>
+      <c r="L18" s="24"/>
+      <c r="M18" s="19"/>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19">
+        <v>8002</v>
+      </c>
+      <c r="F19" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="G19" s="20"/>
+      <c r="H19" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="I19" s="20">
+        <v>22804</v>
+      </c>
+      <c r="J19" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="39">
-        <v>24002</v>
-      </c>
-      <c r="H5" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="19">
-        <v>1</v>
-      </c>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-    </row>
-    <row r="6" ht="15" spans="1:11">
-      <c r="A6" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="31">
-        <v>8001</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="19"/>
-      <c r="F6" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="39">
-        <v>24004</v>
-      </c>
-      <c r="H6" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="I6" s="19">
-        <v>1</v>
-      </c>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
-    </row>
-    <row r="7" s="1" customFormat="1" ht="15" spans="1:11">
-      <c r="A7" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="31">
-        <v>8001</v>
-      </c>
-      <c r="D7" s="20" t="s">
+      <c r="K19" s="20">
+        <v>1</v>
+      </c>
+      <c r="L19" s="24"/>
+      <c r="M19" s="19"/>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19">
+        <v>8002</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="G20" s="20"/>
+      <c r="H20" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="I20" s="20">
+        <v>22805</v>
+      </c>
+      <c r="J20" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="K20" s="20">
+        <v>1</v>
+      </c>
+      <c r="L20" s="24"/>
+      <c r="M20" s="19"/>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" s="49" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" s="50"/>
+      <c r="E21" s="50">
+        <v>8002</v>
+      </c>
+      <c r="F21" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="G21" s="20"/>
+      <c r="H21" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="I21" s="20">
+        <v>22806</v>
+      </c>
+      <c r="J21" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="K21" s="20">
+        <v>1</v>
+      </c>
+      <c r="L21" s="52"/>
+      <c r="M21" s="50"/>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25">
+        <v>8002</v>
+      </c>
+      <c r="F22" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="I22" s="25">
+        <v>22812</v>
+      </c>
+      <c r="J22" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="20"/>
-      <c r="F7" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" s="39">
-        <v>24008</v>
-      </c>
-      <c r="H7" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="I7" s="19">
-        <v>1</v>
-      </c>
-      <c r="J7" s="19"/>
-      <c r="K7" s="19"/>
-    </row>
-    <row r="8" s="1" customFormat="1" ht="15" spans="1:11">
-      <c r="A8" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="31">
-        <v>8001</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="20"/>
-      <c r="F8" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="39">
-        <v>24009</v>
-      </c>
-      <c r="H8" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="I8" s="19">
-        <v>1</v>
-      </c>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19"/>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="15" spans="1:11">
-      <c r="A9" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="31">
-        <v>8001</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="20"/>
-      <c r="F9" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" s="39">
-        <v>24039</v>
-      </c>
-      <c r="H9" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="I9" s="19">
-        <v>1</v>
-      </c>
-      <c r="J9" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="K9" s="19"/>
-    </row>
-    <row r="10" ht="15" spans="1:11">
-      <c r="A10" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="31">
-        <v>8001</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="20"/>
-      <c r="F10" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G10" s="39">
-        <v>24031</v>
-      </c>
-      <c r="H10" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="I10" s="20">
-        <v>1</v>
-      </c>
-      <c r="J10" s="24" t="s">
+      <c r="K22" s="20">
+        <v>1</v>
+      </c>
+      <c r="L22" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="M22" s="19"/>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25">
+        <v>8002</v>
+      </c>
+      <c r="F23" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="G23" s="25"/>
+      <c r="H23" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="I23" s="25">
+        <v>22814</v>
+      </c>
+      <c r="J23" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="K23" s="20">
+        <v>1</v>
+      </c>
+      <c r="L23" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="K10" s="19"/>
-    </row>
-    <row r="11" ht="15" spans="1:11">
-      <c r="A11" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="31">
-        <v>8001</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11" s="19"/>
-      <c r="F11" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" s="39">
-        <v>24012</v>
-      </c>
-      <c r="H11" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="I11" s="20">
-        <v>1</v>
-      </c>
-      <c r="J11" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="K11" s="19"/>
-    </row>
-    <row r="12" ht="15" spans="1:11">
-      <c r="A12" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="31">
-        <v>8001</v>
-      </c>
-      <c r="D12" s="18" t="s">
+      <c r="M23" s="19"/>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25">
+        <v>8002</v>
+      </c>
+      <c r="F24" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="I24" s="25">
+        <v>22816</v>
+      </c>
+      <c r="J24" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="K24" s="20">
+        <v>1</v>
+      </c>
+      <c r="L24" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="20"/>
-      <c r="F12" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="G12" s="42">
-        <v>24070</v>
-      </c>
-      <c r="H12" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="20">
-        <v>18</v>
-      </c>
-      <c r="J12" s="24"/>
-      <c r="K12" s="44"/>
-    </row>
-    <row r="13" ht="15" spans="1:11">
-      <c r="A13" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="31">
-        <v>8001</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" s="20"/>
-      <c r="F13" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="G13" s="42">
-        <v>24090</v>
-      </c>
-      <c r="H13" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="I13" s="20">
-        <v>18</v>
-      </c>
-      <c r="J13" s="24"/>
-      <c r="K13" s="44"/>
-    </row>
-    <row r="14" ht="14.25" spans="1:11">
-      <c r="A14" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="19">
+      <c r="M24" s="19"/>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25">
         <v>8002</v>
       </c>
-      <c r="D14" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="H14" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="I14" s="20">
-        <v>1</v>
-      </c>
-      <c r="J14" s="24"/>
-      <c r="K14" s="19"/>
-    </row>
-    <row r="15" ht="14.25" spans="1:11">
-      <c r="A15" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="19">
+      <c r="F25" s="48" t="s">
+        <v>50</v>
+      </c>
+      <c r="G25" s="20"/>
+      <c r="H25" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="I25" s="20">
+        <v>22818</v>
+      </c>
+      <c r="J25" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="L25" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="M25" s="19"/>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19">
         <v>8002</v>
       </c>
-      <c r="D15" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="E15" s="20"/>
-      <c r="F15" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="G15" s="20">
-        <v>22882</v>
-      </c>
-      <c r="H15" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="20">
-        <v>32</v>
-      </c>
-      <c r="J15" s="18"/>
-      <c r="K15" s="39"/>
-    </row>
-    <row r="16" ht="14.25" spans="1:11">
-      <c r="A16" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" s="19">
+      <c r="F26" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="G26" s="20"/>
+      <c r="H26" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="I26" s="20">
+        <v>22832</v>
+      </c>
+      <c r="J26" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="K26" s="20">
+        <v>1</v>
+      </c>
+      <c r="L26" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="M26" s="19"/>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19">
         <v>8002</v>
       </c>
-      <c r="D16" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="E16" s="20"/>
-      <c r="F16" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G16" s="20">
-        <v>22800</v>
-      </c>
-      <c r="H16" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="I16" s="20">
-        <v>1</v>
-      </c>
-      <c r="J16" s="40"/>
-      <c r="K16" s="19"/>
-    </row>
-    <row r="17" s="38" customFormat="1" ht="14.25" spans="1:11">
-      <c r="A17" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" s="19">
+      <c r="F27" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G27" s="20"/>
+      <c r="H27" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="I27" s="20">
+        <v>22834</v>
+      </c>
+      <c r="J27" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="K27" s="20">
+        <v>1</v>
+      </c>
+      <c r="L27" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="M27" s="19"/>
+    </row>
+    <row r="28" spans="1:13">
+      <c r="A28" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19">
         <v>8002</v>
       </c>
-      <c r="D17" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="E17" s="20"/>
-      <c r="F17" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G17" s="20">
-        <v>22801</v>
-      </c>
-      <c r="H17" s="46" t="s">
-        <v>24</v>
-      </c>
-      <c r="I17" s="20">
-        <v>1</v>
-      </c>
-      <c r="J17" s="24"/>
-      <c r="K17" s="19"/>
-    </row>
-    <row r="18" s="38" customFormat="1" ht="14.25" spans="1:11">
-      <c r="A18" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" s="19">
+      <c r="F28" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="G28" s="20"/>
+      <c r="H28" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="I28" s="20">
+        <v>22839</v>
+      </c>
+      <c r="J28" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="K28" s="20">
+        <v>1</v>
+      </c>
+      <c r="L28" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="M28" s="19"/>
+    </row>
+    <row r="29" spans="1:13">
+      <c r="A29" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C29" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19">
         <v>8002</v>
       </c>
-      <c r="D18" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="E18" s="20"/>
-      <c r="F18" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G18" s="20">
-        <v>22802</v>
-      </c>
-      <c r="H18" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="I18" s="20">
-        <v>1</v>
-      </c>
-      <c r="J18" s="24"/>
-      <c r="K18" s="19"/>
-    </row>
-    <row r="19" ht="14.25" spans="1:11">
-      <c r="A19" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" s="19">
+      <c r="F29" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="G29" s="20"/>
+      <c r="H29" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="I29" s="20">
+        <v>22842</v>
+      </c>
+      <c r="J29" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="K29" s="20">
+        <v>1</v>
+      </c>
+      <c r="L29" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="M29" s="19"/>
+    </row>
+    <row r="30" spans="1:13">
+      <c r="A30" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19">
         <v>8002</v>
       </c>
-      <c r="D19" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="E19" s="20"/>
-      <c r="F19" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G19" s="20">
-        <v>22804</v>
-      </c>
-      <c r="H19" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="I19" s="20">
-        <v>1</v>
-      </c>
-      <c r="J19" s="24"/>
-      <c r="K19" s="19"/>
-    </row>
-    <row r="20" ht="14.25" spans="1:11">
-      <c r="A20" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B20" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20" s="19">
+      <c r="F30" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="G30" s="20"/>
+      <c r="H30" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="I30" s="20">
+        <v>22845</v>
+      </c>
+      <c r="J30" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="K30" s="20">
+        <v>1</v>
+      </c>
+      <c r="L30" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="M30" s="19"/>
+    </row>
+    <row r="31" spans="1:13">
+      <c r="A31" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19">
         <v>8002</v>
       </c>
-      <c r="D20" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="E20" s="20"/>
-      <c r="F20" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G20" s="20">
-        <v>22805</v>
-      </c>
-      <c r="H20" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="I20" s="20">
-        <v>1</v>
-      </c>
-      <c r="J20" s="24"/>
-      <c r="K20" s="19"/>
-    </row>
-    <row r="21" ht="14.25" spans="1:11">
-      <c r="A21" s="47" t="s">
-        <v>34</v>
-      </c>
-      <c r="B21" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="C21" s="49">
+      <c r="F31" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="G31" s="20"/>
+      <c r="H31" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="I31" s="53">
+        <v>22848</v>
+      </c>
+      <c r="J31" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="K31" s="20">
+        <v>1</v>
+      </c>
+      <c r="L31" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="M31" s="19"/>
+    </row>
+    <row r="32" customFormat="1" ht="14.25" spans="1:13">
+      <c r="A32" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D32" s="25"/>
+      <c r="E32" s="25">
         <v>8002</v>
       </c>
-      <c r="D21" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="E21" s="20"/>
-      <c r="F21" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="G21" s="20">
-        <v>22806</v>
-      </c>
-      <c r="H21" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="I21" s="20">
-        <v>1</v>
-      </c>
-      <c r="J21" s="51"/>
-      <c r="K21" s="49"/>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="A22" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B22" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C22" s="25">
+      <c r="F32" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="G32" s="25"/>
+      <c r="H32" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="I32" s="25">
+        <v>22856</v>
+      </c>
+      <c r="J32" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="K32" s="20">
+        <v>1</v>
+      </c>
+      <c r="L32" s="25"/>
+      <c r="M32" s="19"/>
+    </row>
+    <row r="33" customFormat="1" ht="14.25" spans="1:13">
+      <c r="A33" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25">
         <v>8002</v>
       </c>
-      <c r="D22" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="G22" s="25">
-        <v>22812</v>
-      </c>
-      <c r="H22" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I22" s="20">
-        <v>1</v>
-      </c>
-      <c r="J22" s="24" t="s">
+      <c r="F33" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="I33" s="25">
+        <v>22858</v>
+      </c>
+      <c r="J33" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="K33" s="20">
+        <v>1</v>
+      </c>
+      <c r="L33" s="25"/>
+      <c r="M33" s="19"/>
+    </row>
+    <row r="34" customFormat="1" ht="14.25" spans="1:13">
+      <c r="A34" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C34" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25">
+        <v>8002</v>
+      </c>
+      <c r="F34" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="G34" s="25"/>
+      <c r="H34" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="I34" s="25">
+        <v>22860</v>
+      </c>
+      <c r="J34" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="K34" s="20">
+        <v>1</v>
+      </c>
+      <c r="L34" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="M34" s="19"/>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C35" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D35" s="25"/>
+      <c r="E35" s="25">
+        <v>8002</v>
+      </c>
+      <c r="F35" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="G35" s="25"/>
+      <c r="H35" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="I35" s="25">
+        <v>22874</v>
+      </c>
+      <c r="J35" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="K35" s="20">
+        <v>1</v>
+      </c>
+      <c r="L35" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="K22" s="19"/>
-    </row>
-    <row r="23" ht="14.25" spans="1:11">
-      <c r="A23" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B23" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C23" s="25">
+      <c r="M35" s="19"/>
+    </row>
+    <row r="36" spans="1:13">
+      <c r="A36" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C36" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D36" s="25"/>
+      <c r="E36" s="25">
         <v>8002</v>
       </c>
-      <c r="D23" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="E23" s="25"/>
-      <c r="F23" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="G23" s="25">
-        <v>22814</v>
-      </c>
-      <c r="H23" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I23" s="20">
-        <v>1</v>
-      </c>
-      <c r="J23" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="K23" s="19"/>
-    </row>
-    <row r="24" ht="14.25" spans="1:11">
-      <c r="A24" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C24" s="25">
+      <c r="F36" s="54" t="s">
+        <v>62</v>
+      </c>
+      <c r="G36" s="25"/>
+      <c r="H36" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="I36" s="25">
+        <v>22875</v>
+      </c>
+      <c r="J36" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="K36" s="20">
+        <v>1</v>
+      </c>
+      <c r="L36" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="M36" s="19"/>
+    </row>
+    <row r="37" ht="27.75" spans="1:13">
+      <c r="A37" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C37" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D37" s="25"/>
+      <c r="E37" s="25">
         <v>8002</v>
       </c>
-      <c r="D24" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="E24" s="25"/>
-      <c r="F24" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="G24" s="25">
-        <v>22816</v>
-      </c>
-      <c r="H24" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I24" s="20">
-        <v>1</v>
-      </c>
-      <c r="J24" s="24" t="s">
+      <c r="F37" s="54" t="s">
+        <v>63</v>
+      </c>
+      <c r="G37" s="25"/>
+      <c r="H37" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="I37" s="25">
+        <v>22876</v>
+      </c>
+      <c r="J37" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="K37" s="20">
+        <v>1</v>
+      </c>
+      <c r="L37" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="K24" s="19"/>
-    </row>
-    <row r="25" ht="14.25" spans="1:11">
-      <c r="A25" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B25" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C25" s="25">
+      <c r="M37" s="19"/>
+    </row>
+    <row r="38" ht="27.75" spans="1:13">
+      <c r="A38" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C38" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D38" s="25"/>
+      <c r="E38" s="25">
         <v>8002</v>
       </c>
-      <c r="D25" s="47" t="s">
-        <v>48</v>
-      </c>
-      <c r="E25" s="20"/>
-      <c r="F25" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G25" s="20">
+      <c r="F38" s="54" t="s">
+        <v>64</v>
+      </c>
+      <c r="G38" s="25"/>
+      <c r="H38" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="I38" s="25">
+        <v>22877</v>
+      </c>
+      <c r="J38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="K38" s="20">
+        <v>1</v>
+      </c>
+      <c r="L38" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="M38" s="19"/>
+    </row>
+    <row r="39" spans="1:13">
+      <c r="A39" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B39" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C39" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D39" s="25"/>
+      <c r="E39" s="25">
+        <v>8002</v>
+      </c>
+      <c r="F39" s="54" t="s">
+        <v>65</v>
+      </c>
+      <c r="G39" s="25"/>
+      <c r="H39" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="I39" s="25">
+        <v>22878</v>
+      </c>
+      <c r="J39" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="K39" s="20">
+        <v>1</v>
+      </c>
+      <c r="L39" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="M39" s="19"/>
+    </row>
+    <row r="40" spans="1:13">
+      <c r="A40" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B40" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C40" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D40" s="25"/>
+      <c r="E40" s="25">
+        <v>8002</v>
+      </c>
+      <c r="F40" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="G40" s="25"/>
+      <c r="H40" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="I40" s="25">
+        <v>22879</v>
+      </c>
+      <c r="J40" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="K40" s="20">
+        <v>1</v>
+      </c>
+      <c r="L40" s="25"/>
+      <c r="M40" s="19"/>
+    </row>
+    <row r="41" ht="15" spans="1:13">
+      <c r="A41" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B41" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C41" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D41" s="25"/>
+      <c r="E41" s="25">
+        <v>8002</v>
+      </c>
+      <c r="F41" s="54" t="s">
+        <v>67</v>
+      </c>
+      <c r="G41" s="25"/>
+      <c r="H41" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="I41" s="25">
+        <v>22902</v>
+      </c>
+      <c r="J41" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="K41" s="20">
+        <v>1</v>
+      </c>
+      <c r="L41" s="25"/>
+      <c r="M41" s="19"/>
+    </row>
+    <row r="42" spans="1:13">
+      <c r="A42" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D42" s="25"/>
+      <c r="E42" s="25">
+        <v>8002</v>
+      </c>
+      <c r="F42" s="54" t="s">
+        <v>68</v>
+      </c>
+      <c r="G42" s="25"/>
+      <c r="H42" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="I42" s="25">
+        <v>22856</v>
+      </c>
+      <c r="J42" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="K42" s="20">
+        <v>1</v>
+      </c>
+      <c r="L42" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="M42" s="19"/>
+    </row>
+    <row r="43" spans="1:13">
+      <c r="A43" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B43" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C43" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D43" s="25"/>
+      <c r="E43" s="25">
+        <v>8002</v>
+      </c>
+      <c r="F43" s="54" t="s">
+        <v>69</v>
+      </c>
+      <c r="G43" s="25"/>
+      <c r="H43" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="I43" s="25">
+        <v>22858</v>
+      </c>
+      <c r="J43" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="K43" s="20">
+        <v>1</v>
+      </c>
+      <c r="L43" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="M43" s="19"/>
+    </row>
+    <row r="44" spans="1:13">
+      <c r="A44" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C44" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D44" s="25"/>
+      <c r="E44" s="25">
+        <v>8002</v>
+      </c>
+      <c r="F44" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="G44" s="25"/>
+      <c r="H44" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="I44" s="25">
         <v>22818</v>
       </c>
-      <c r="H25" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="J25" s="24" t="s">
+      <c r="J44" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="K44" s="20">
+        <v>1</v>
+      </c>
+      <c r="L44" s="25"/>
+      <c r="M44" s="19"/>
+    </row>
+    <row r="45" spans="1:13">
+      <c r="A45" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B45" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C45" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D45" s="25"/>
+      <c r="E45" s="25">
+        <v>8002</v>
+      </c>
+      <c r="F45" s="54" t="s">
+        <v>71</v>
+      </c>
+      <c r="G45" s="25"/>
+      <c r="H45" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="I45" s="25">
+        <v>22854</v>
+      </c>
+      <c r="J45" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="K45" s="20">
+        <v>1</v>
+      </c>
+      <c r="L45" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="K25" s="19"/>
-    </row>
-    <row r="26" ht="14.25" spans="1:11">
-      <c r="A26" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C26" s="19">
+      <c r="M45" s="19"/>
+    </row>
+    <row r="46" spans="1:13">
+      <c r="A46" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B46" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C46" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D46" s="25"/>
+      <c r="E46" s="25">
         <v>8002</v>
       </c>
-      <c r="D26" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="E26" s="20"/>
-      <c r="F26" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G26" s="20">
-        <v>22832</v>
-      </c>
-      <c r="H26" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="I26" s="20">
-        <v>1</v>
-      </c>
-      <c r="J26" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="K26" s="19"/>
-    </row>
-    <row r="27" ht="14.25" spans="1:11">
-      <c r="A27" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" s="19">
+      <c r="F46" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="G46" s="19"/>
+      <c r="H46" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="I46" s="39">
+        <v>20005</v>
+      </c>
+      <c r="J46" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="K46" s="20">
+        <v>1</v>
+      </c>
+      <c r="L46" s="19"/>
+      <c r="M46" s="19"/>
+    </row>
+    <row r="47" spans="1:13">
+      <c r="A47" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B47" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C47" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D47" s="25"/>
+      <c r="E47" s="25">
         <v>8002</v>
       </c>
-      <c r="D27" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="E27" s="20"/>
-      <c r="F27" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G27" s="20">
-        <v>22834</v>
-      </c>
-      <c r="H27" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="I27" s="20">
-        <v>1</v>
-      </c>
-      <c r="J27" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="K27" s="19"/>
-    </row>
-    <row r="28" ht="14.25" spans="1:11">
-      <c r="A28" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B28" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C28" s="19">
-        <v>8002</v>
-      </c>
-      <c r="D28" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="E28" s="20"/>
-      <c r="F28" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G28" s="20">
-        <v>22839</v>
-      </c>
-      <c r="H28" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="I28" s="20">
-        <v>1</v>
-      </c>
-      <c r="J28" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="K28" s="19"/>
-    </row>
-    <row r="29" ht="14.25" spans="1:11">
-      <c r="A29" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B29" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="C29" s="19">
-        <v>8002</v>
-      </c>
-      <c r="D29" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="E29" s="20"/>
-      <c r="F29" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G29" s="20">
-        <v>22842</v>
-      </c>
-      <c r="H29" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="I29" s="20">
-        <v>1</v>
-      </c>
-      <c r="J29" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="K29" s="19"/>
-    </row>
-    <row r="30" ht="14.25" spans="1:11">
-      <c r="A30" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C30" s="19">
-        <v>8002</v>
-      </c>
-      <c r="D30" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="E30" s="20"/>
-      <c r="F30" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G30" s="20">
-        <v>22845</v>
-      </c>
-      <c r="H30" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="I30" s="20">
-        <v>1</v>
-      </c>
-      <c r="J30" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="K30" s="19"/>
-    </row>
-    <row r="31" ht="14.25" spans="1:11">
-      <c r="A31" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B31" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C31" s="19">
-        <v>8002</v>
-      </c>
-      <c r="D31" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="E31" s="20"/>
-      <c r="F31" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G31" s="52">
-        <v>22848</v>
-      </c>
-      <c r="H31" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="I31" s="20">
-        <v>1</v>
-      </c>
-      <c r="J31" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="K31" s="19"/>
-    </row>
-    <row r="32" customFormat="1" ht="14.25" spans="1:11">
-      <c r="A32" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B32" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C32" s="25">
-        <v>8002</v>
-      </c>
-      <c r="D32" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="E32" s="25"/>
-      <c r="F32" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="G32" s="25">
-        <v>22856</v>
-      </c>
-      <c r="H32" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I32" s="20">
-        <v>1</v>
-      </c>
-      <c r="J32" s="25"/>
-      <c r="K32" s="19"/>
-    </row>
-    <row r="33" customFormat="1" ht="14.25" spans="1:11">
-      <c r="A33" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B33" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C33" s="25">
-        <v>8002</v>
-      </c>
-      <c r="D33" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="E33" s="25"/>
-      <c r="F33" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="G33" s="25">
-        <v>22858</v>
-      </c>
-      <c r="H33" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I33" s="20">
-        <v>1</v>
-      </c>
-      <c r="J33" s="25"/>
-      <c r="K33" s="19"/>
-    </row>
-    <row r="34" customFormat="1" ht="14.25" spans="1:11">
-      <c r="A34" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B34" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C34" s="25">
-        <v>8002</v>
-      </c>
-      <c r="D34" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="G34" s="25">
-        <v>22860</v>
-      </c>
-      <c r="H34" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I34" s="20">
-        <v>1</v>
-      </c>
-      <c r="J34" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="K34" s="19"/>
-    </row>
-    <row r="35" ht="14.25" spans="1:11">
-      <c r="A35" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B35" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C35" s="25">
-        <v>8002</v>
-      </c>
-      <c r="D35" s="53" t="s">
-        <v>59</v>
-      </c>
-      <c r="E35" s="25"/>
-      <c r="F35" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="G35" s="25">
-        <v>22874</v>
-      </c>
-      <c r="H35" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="I35" s="20">
-        <v>1</v>
-      </c>
-      <c r="J35" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="K35" s="19"/>
-    </row>
-    <row r="36" ht="14.25" spans="1:11">
-      <c r="A36" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B36" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C36" s="25">
-        <v>8002</v>
-      </c>
-      <c r="D36" s="53" t="s">
-        <v>60</v>
-      </c>
-      <c r="E36" s="25"/>
-      <c r="F36" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="G36" s="25">
-        <v>22875</v>
-      </c>
-      <c r="H36" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="I36" s="20">
-        <v>1</v>
-      </c>
-      <c r="J36" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="K36" s="19"/>
-    </row>
-    <row r="37" ht="27.75" spans="1:11">
-      <c r="A37" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B37" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C37" s="25">
-        <v>8002</v>
-      </c>
-      <c r="D37" s="53" t="s">
-        <v>61</v>
-      </c>
-      <c r="E37" s="25"/>
-      <c r="F37" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="G37" s="25">
-        <v>22876</v>
-      </c>
-      <c r="H37" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="I37" s="20">
-        <v>1</v>
-      </c>
-      <c r="J37" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="K37" s="19"/>
-    </row>
-    <row r="38" ht="27.75" spans="1:11">
-      <c r="A38" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B38" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C38" s="25">
-        <v>8002</v>
-      </c>
-      <c r="D38" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="E38" s="25"/>
-      <c r="F38" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="G38" s="25">
-        <v>22877</v>
-      </c>
-      <c r="H38" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="I38" s="20">
-        <v>1</v>
-      </c>
-      <c r="J38" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="K38" s="19"/>
-    </row>
-    <row r="39" ht="14.25" spans="1:11">
-      <c r="A39" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B39" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C39" s="25">
-        <v>8002</v>
-      </c>
-      <c r="D39" s="53" t="s">
-        <v>63</v>
-      </c>
-      <c r="E39" s="25"/>
-      <c r="F39" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="G39" s="25">
-        <v>22878</v>
-      </c>
-      <c r="H39" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="I39" s="20">
-        <v>1</v>
-      </c>
-      <c r="J39" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="K39" s="19"/>
-    </row>
-    <row r="40" ht="14.25" spans="1:11">
-      <c r="A40" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B40" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C40" s="25">
-        <v>8002</v>
-      </c>
-      <c r="D40" s="53" t="s">
-        <v>64</v>
-      </c>
-      <c r="E40" s="25"/>
-      <c r="F40" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="G40" s="25">
-        <v>22879</v>
-      </c>
-      <c r="H40" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="I40" s="20">
-        <v>1</v>
-      </c>
-      <c r="J40" s="25"/>
-      <c r="K40" s="19"/>
-    </row>
-    <row r="41" ht="15" spans="1:11">
-      <c r="A41" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B41" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C41" s="25">
-        <v>8002</v>
-      </c>
-      <c r="D41" s="53" t="s">
-        <v>65</v>
-      </c>
-      <c r="E41" s="25"/>
-      <c r="F41" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="G41" s="25">
-        <v>22902</v>
-      </c>
-      <c r="H41" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="I41" s="20">
-        <v>1</v>
-      </c>
-      <c r="J41" s="25"/>
-      <c r="K41" s="19"/>
-    </row>
-    <row r="42" ht="14.25" spans="1:11">
-      <c r="A42" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B42" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C42" s="25">
-        <v>8002</v>
-      </c>
-      <c r="D42" s="53" t="s">
-        <v>66</v>
-      </c>
-      <c r="E42" s="25"/>
-      <c r="F42" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="G42" s="25">
-        <v>22856</v>
-      </c>
-      <c r="H42" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I42" s="20">
-        <v>1</v>
-      </c>
-      <c r="J42" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="K42" s="19"/>
-    </row>
-    <row r="43" ht="14.25" spans="1:11">
-      <c r="A43" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B43" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C43" s="25">
-        <v>8002</v>
-      </c>
-      <c r="D43" s="53" t="s">
-        <v>67</v>
-      </c>
-      <c r="E43" s="25"/>
-      <c r="F43" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="G43" s="25">
-        <v>22858</v>
-      </c>
-      <c r="H43" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I43" s="20">
-        <v>1</v>
-      </c>
-      <c r="J43" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="K43" s="19"/>
-    </row>
-    <row r="44" ht="14.25" spans="1:11">
-      <c r="A44" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B44" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C44" s="25">
-        <v>8002</v>
-      </c>
-      <c r="D44" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="E44" s="25"/>
-      <c r="F44" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="G44" s="25">
-        <v>22818</v>
-      </c>
-      <c r="H44" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I44" s="20">
-        <v>1</v>
-      </c>
-      <c r="J44" s="25"/>
-      <c r="K44" s="19"/>
-    </row>
-    <row r="45" ht="14.25" spans="1:11">
-      <c r="A45" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B45" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C45" s="25">
-        <v>8002</v>
-      </c>
-      <c r="D45" s="53" t="s">
-        <v>69</v>
-      </c>
-      <c r="E45" s="25"/>
-      <c r="F45" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="G45" s="25">
-        <v>22854</v>
-      </c>
-      <c r="H45" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I45" s="20">
-        <v>1</v>
-      </c>
-      <c r="J45" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="K45" s="19"/>
-    </row>
-    <row r="46" ht="14.25" spans="1:11">
-      <c r="A46" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B46" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C46" s="25">
-        <v>8002</v>
-      </c>
-      <c r="D46" s="39" t="s">
-        <v>70</v>
-      </c>
-      <c r="E46" s="19"/>
-      <c r="F46" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="G46" s="39">
-        <v>20005</v>
-      </c>
-      <c r="H46" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="I46" s="20">
-        <v>1</v>
-      </c>
-      <c r="J46" s="19"/>
-      <c r="K46" s="19"/>
-    </row>
-    <row r="47" ht="14.25" spans="1:11">
-      <c r="A47" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B47" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C47" s="25">
-        <v>8002</v>
-      </c>
-      <c r="D47" s="39" t="s">
-        <v>71</v>
-      </c>
-      <c r="E47" s="19"/>
-      <c r="F47" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="G47" s="39">
+      <c r="F47" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="G47" s="19"/>
+      <c r="H47" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="I47" s="39">
         <v>20000</v>
       </c>
-      <c r="H47" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="I47" s="20">
-        <v>1</v>
-      </c>
-      <c r="J47" s="19"/>
-      <c r="K47" s="19"/>
+      <c r="J47" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="K47" s="20">
+        <v>1</v>
+      </c>
+      <c r="L47" s="19"/>
+      <c r="M47" s="19"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:N47" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:P47" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2975,24 +3175,24 @@
     <row r="1" ht="14.25"/>
     <row r="2" s="1" customFormat="1" ht="14.25" spans="1:12">
       <c r="A2" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C2" s="6">
         <v>9004</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E2" s="7"/>
       <c r="F2" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G2" s="7"/>
       <c r="H2" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I2" s="7">
         <v>1</v>
@@ -3003,24 +3203,24 @@
     </row>
     <row r="3" s="1" customFormat="1" ht="14.25" spans="1:12">
       <c r="A3" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C3" s="6">
         <v>9004</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E3" s="7"/>
       <c r="F3" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G3" s="7"/>
       <c r="H3" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I3" s="7">
         <v>1</v>
@@ -3031,24 +3231,24 @@
     </row>
     <row r="4" s="2" customFormat="1" ht="14.25" spans="1:12">
       <c r="A4" s="12" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C4" s="13">
         <v>9004</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G4" s="13"/>
       <c r="H4" s="14" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I4" s="7">
         <v>1</v>
@@ -3060,24 +3260,24 @@
     <row r="5" customFormat="1" ht="14.25" hidden="1"/>
     <row r="6" ht="14.25" spans="1:12">
       <c r="A6" s="17" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C6" s="19">
         <v>9004</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E6" s="20"/>
       <c r="F6" s="17" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G6" s="20"/>
       <c r="H6" s="21" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I6" s="20">
         <v>1</v>
@@ -3088,24 +3288,24 @@
     </row>
     <row r="7" ht="14.25" spans="1:12">
       <c r="A7" s="17" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C7" s="19">
         <v>9004</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E7" s="20"/>
       <c r="F7" s="17" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G7" s="20"/>
       <c r="H7" s="21" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I7" s="20">
         <v>1</v>
@@ -3116,24 +3316,24 @@
     </row>
     <row r="8" ht="14.25" spans="1:12">
       <c r="A8" s="17" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C8" s="19">
         <v>9004</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E8" s="20"/>
       <c r="F8" s="17" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G8" s="20"/>
       <c r="H8" s="21" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I8" s="20">
         <v>1</v>
@@ -3144,144 +3344,144 @@
     </row>
     <row r="9" ht="14.25" spans="1:12">
       <c r="A9" s="17" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C9" s="19">
         <v>9004</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E9" s="20"/>
       <c r="F9" s="17" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="21" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I9" s="20">
         <v>1</v>
       </c>
       <c r="J9" s="22" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K9" s="23"/>
       <c r="L9" s="19"/>
     </row>
     <row r="10" ht="14.25" spans="1:12">
       <c r="A10" s="17" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C10" s="19">
         <v>9004</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E10" s="20"/>
       <c r="F10" s="17" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G10" s="20"/>
       <c r="H10" s="21" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I10" s="20">
         <v>1</v>
       </c>
       <c r="J10" s="22" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K10" s="23"/>
       <c r="L10" s="19"/>
     </row>
     <row r="11" ht="14.25" spans="1:12">
       <c r="A11" s="17" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C11" s="19">
         <v>9004</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E11" s="20"/>
       <c r="F11" s="17" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G11" s="20"/>
       <c r="H11" s="21" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I11" s="20">
         <v>1</v>
       </c>
       <c r="J11" s="22" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K11" s="23"/>
       <c r="L11" s="19"/>
     </row>
     <row r="12" ht="14.25" spans="1:12">
       <c r="A12" s="17" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C12" s="19">
         <v>9004</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E12" s="20"/>
       <c r="F12" s="17" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G12" s="20"/>
       <c r="H12" s="21" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I12" s="20">
         <v>1</v>
       </c>
       <c r="J12" s="22" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K12" s="23"/>
       <c r="L12" s="19"/>
     </row>
     <row r="13" ht="14.25" spans="1:12">
       <c r="A13" s="25" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C13" s="19">
         <v>9004</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E13" s="20"/>
       <c r="F13" s="18" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G13" s="24"/>
       <c r="H13" s="26" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I13" s="18">
         <v>1</v>
@@ -3292,16 +3492,16 @@
     </row>
     <row r="14" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A14" s="12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C14" s="29">
         <v>8001</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
@@ -3313,16 +3513,16 @@
     </row>
     <row r="15" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A15" s="12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C15" s="29">
         <v>8001</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
@@ -3334,16 +3534,16 @@
     </row>
     <row r="16" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A16" s="12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C16" s="29">
         <v>8001</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
@@ -3355,16 +3555,16 @@
     </row>
     <row r="17" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A17" s="12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C17" s="29">
         <v>8001</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
@@ -3376,16 +3576,16 @@
     </row>
     <row r="18" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A18" s="12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C18" s="29">
         <v>8001</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
@@ -3397,16 +3597,16 @@
     </row>
     <row r="19" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A19" s="12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C19" s="29">
         <v>8001</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
@@ -3418,16 +3618,16 @@
     </row>
     <row r="20" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A20" s="12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C20" s="29">
         <v>8001</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
@@ -3439,16 +3639,16 @@
     </row>
     <row r="21" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A21" s="12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C21" s="29">
         <v>8001</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
@@ -3460,16 +3660,16 @@
     </row>
     <row r="22" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A22" s="12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C22" s="29">
         <v>8001</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
@@ -3481,16 +3681,16 @@
     </row>
     <row r="23" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A23" s="12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C23" s="29">
         <v>8001</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
@@ -3502,16 +3702,16 @@
     </row>
     <row r="24" s="1" customFormat="1" ht="15" hidden="1" spans="1:12">
       <c r="A24" s="12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C24" s="29">
         <v>8001</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
@@ -3523,23 +3723,23 @@
     </row>
     <row r="25" ht="15" hidden="1" spans="1:12">
       <c r="A25" s="25" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C25" s="31">
         <v>8001</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F25" s="18" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G25" s="24"/>
       <c r="H25" s="26" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I25" s="18">
         <v>1</v>
@@ -3550,30 +3750,30 @@
     </row>
     <row r="26" s="3" customFormat="1" ht="14.25" spans="1:12">
       <c r="A26" s="32" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B26" s="33" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C26" s="34">
         <v>9004</v>
       </c>
       <c r="D26" s="35" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E26" s="35"/>
       <c r="F26" s="32" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G26" s="35"/>
       <c r="H26" s="36" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I26" s="35">
         <v>1</v>
       </c>
       <c r="J26" s="37" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
